--- a/average_levels.xlsx
+++ b/average_levels.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -47,6 +47,11 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -60,12 +65,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -431,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J379"/>
+  <dimension ref="A1:K380"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -442,8 +448,9 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -484,15 +491,20 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Corners interpolated</t>
+          <t>Corners at hangar level</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Corners interpolated (TIN)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>X min</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Y min</t>
         </is>
@@ -524,9 +536,12 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
         <v>353767.166</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>355982.049</v>
       </c>
     </row>
@@ -556,9 +571,12 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
         <v>353770.166</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>355982.049</v>
       </c>
     </row>
@@ -588,9 +606,12 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
         <v>353773.166</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>355982.049</v>
       </c>
     </row>
@@ -620,9 +641,12 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
         <v>353776.166</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>355982.049</v>
       </c>
     </row>
@@ -652,9 +676,12 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
         <v>353752.166</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>355979.049</v>
       </c>
     </row>
@@ -684,9 +711,12 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
         <v>353755.166</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>355979.049</v>
       </c>
     </row>
@@ -716,9 +746,12 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
         <v>353758.166</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>355979.049</v>
       </c>
     </row>
@@ -748,9 +781,12 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
         <v>353761.166</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>355979.049</v>
       </c>
     </row>
@@ -780,9 +816,12 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
         <v>353764.166</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>355979.049</v>
       </c>
     </row>
@@ -812,9 +851,12 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
         <v>353767.166</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>355979.049</v>
       </c>
     </row>
@@ -844,9 +886,12 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
         <v>353770.166</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>355979.049</v>
       </c>
     </row>
@@ -876,9 +921,12 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
         <v>353773.166</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>355979.049</v>
       </c>
     </row>
@@ -908,9 +956,12 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
         <v>353776.166</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>355979.049</v>
       </c>
     </row>
@@ -940,9 +991,12 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
         <v>353779.166</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>355979.049</v>
       </c>
     </row>
@@ -972,9 +1026,12 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
         <v>353782.166</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>355979.049</v>
       </c>
     </row>
@@ -1004,9 +1061,12 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
         <v>353785.166</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>355979.049</v>
       </c>
     </row>
@@ -1036,9 +1096,12 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
         <v>353788.166</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>355979.049</v>
       </c>
     </row>
@@ -1068,9 +1131,12 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
         <v>353791.166</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>355979.049</v>
       </c>
     </row>
@@ -1100,9 +1166,12 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
         <v>353794.166</v>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>355979.049</v>
       </c>
     </row>
@@ -1132,9 +1201,12 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
         <v>353797.166</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>355979.049</v>
       </c>
     </row>
@@ -1164,9 +1236,12 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
         <v>353752.166</v>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>355976.049</v>
       </c>
     </row>
@@ -1196,9 +1271,12 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
         <v>353755.166</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>355976.049</v>
       </c>
     </row>
@@ -1228,9 +1306,12 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
         <v>353758.166</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>355976.049</v>
       </c>
     </row>
@@ -1260,9 +1341,12 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
         <v>353761.166</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>355976.049</v>
       </c>
     </row>
@@ -1292,9 +1376,12 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
         <v>353764.166</v>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>355976.049</v>
       </c>
     </row>
@@ -1324,9 +1411,12 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
         <v>353767.166</v>
       </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
         <v>355976.049</v>
       </c>
     </row>
@@ -1356,9 +1446,12 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
         <v>353770.166</v>
       </c>
-      <c r="J28" t="n">
+      <c r="K28" t="n">
         <v>355976.049</v>
       </c>
     </row>
@@ -1388,9 +1481,12 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
         <v>353773.166</v>
       </c>
-      <c r="J29" t="n">
+      <c r="K29" t="n">
         <v>355976.049</v>
       </c>
     </row>
@@ -1420,9 +1516,12 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
         <v>353776.166</v>
       </c>
-      <c r="J30" t="n">
+      <c r="K30" t="n">
         <v>355976.049</v>
       </c>
     </row>
@@ -1452,9 +1551,12 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
         <v>353779.166</v>
       </c>
-      <c r="J31" t="n">
+      <c r="K31" t="n">
         <v>355976.049</v>
       </c>
     </row>
@@ -1484,9 +1586,12 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
         <v>353782.166</v>
       </c>
-      <c r="J32" t="n">
+      <c r="K32" t="n">
         <v>355976.049</v>
       </c>
     </row>
@@ -1516,9 +1621,12 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
         <v>353785.166</v>
       </c>
-      <c r="J33" t="n">
+      <c r="K33" t="n">
         <v>355976.049</v>
       </c>
     </row>
@@ -1548,9 +1656,12 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
         <v>353788.166</v>
       </c>
-      <c r="J34" t="n">
+      <c r="K34" t="n">
         <v>355976.049</v>
       </c>
     </row>
@@ -1580,9 +1691,12 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
         <v>353791.166</v>
       </c>
-      <c r="J35" t="n">
+      <c r="K35" t="n">
         <v>355976.049</v>
       </c>
     </row>
@@ -1612,9 +1726,12 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
         <v>353794.166</v>
       </c>
-      <c r="J36" t="n">
+      <c r="K36" t="n">
         <v>355976.049</v>
       </c>
     </row>
@@ -1644,9 +1761,12 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
         <v>353797.166</v>
       </c>
-      <c r="J37" t="n">
+      <c r="K37" t="n">
         <v>355976.049</v>
       </c>
     </row>
@@ -1676,9 +1796,12 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
         <v>353749.166</v>
       </c>
-      <c r="J38" t="n">
+      <c r="K38" t="n">
         <v>355973.049</v>
       </c>
     </row>
@@ -1708,9 +1831,12 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
         <v>353752.166</v>
       </c>
-      <c r="J39" t="n">
+      <c r="K39" t="n">
         <v>355973.049</v>
       </c>
     </row>
@@ -1719,7 +1845,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>1115.658</v>
+        <v>1115.603</v>
       </c>
       <c r="C40" s="2" t="n">
         <v>1115.56</v>
@@ -1728,7 +1854,7 @@
         <v>1115.58</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>1115.77</v>
+        <v>1115.55</v>
       </c>
       <c r="F40" s="2" t="n">
         <v>1115.72</v>
@@ -1740,9 +1866,12 @@
         <v>1</v>
       </c>
       <c r="I40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="2" t="n">
         <v>353755.166</v>
       </c>
-      <c r="J40" s="2" t="n">
+      <c r="K40" s="2" t="n">
         <v>355973.049</v>
       </c>
     </row>
@@ -1751,7 +1880,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>1115.835</v>
+        <v>1115.566</v>
       </c>
       <c r="C41" s="2" t="n">
         <v>1115.58</v>
@@ -1760,10 +1889,10 @@
         <v>1115.58</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>1116.4</v>
+        <v>1115.55</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>1115.77</v>
+        <v>1115.55</v>
       </c>
       <c r="G41" s="2" t="n">
         <v>9</v>
@@ -1772,9 +1901,12 @@
         <v>2</v>
       </c>
       <c r="I41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="2" t="n">
         <v>353758.166</v>
       </c>
-      <c r="J41" s="2" t="n">
+      <c r="K41" s="2" t="n">
         <v>355973.049</v>
       </c>
     </row>
@@ -1783,7 +1915,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>1116.363</v>
+        <v>1116.149</v>
       </c>
       <c r="C42" s="2" t="n">
         <v>1115.58</v>
@@ -1795,7 +1927,7 @@
         <v>1117.13</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>1116.4</v>
+        <v>1115.55</v>
       </c>
       <c r="G42" s="2" t="n">
         <v>9</v>
@@ -1804,9 +1936,12 @@
         <v>1</v>
       </c>
       <c r="I42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="2" t="n">
         <v>353761.166</v>
       </c>
-      <c r="J42" s="2" t="n">
+      <c r="K42" s="2" t="n">
         <v>355973.049</v>
       </c>
     </row>
@@ -1836,9 +1971,12 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
         <v>353764.166</v>
       </c>
-      <c r="J43" t="n">
+      <c r="K43" t="n">
         <v>355973.049</v>
       </c>
     </row>
@@ -1868,9 +2006,12 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
         <v>353767.166</v>
       </c>
-      <c r="J44" t="n">
+      <c r="K44" t="n">
         <v>355973.049</v>
       </c>
     </row>
@@ -1900,9 +2041,12 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
         <v>353770.166</v>
       </c>
-      <c r="J45" t="n">
+      <c r="K45" t="n">
         <v>355973.049</v>
       </c>
     </row>
@@ -1932,9 +2076,12 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
         <v>353773.166</v>
       </c>
-      <c r="J46" t="n">
+      <c r="K46" t="n">
         <v>355973.049</v>
       </c>
     </row>
@@ -1964,9 +2111,12 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
         <v>353776.166</v>
       </c>
-      <c r="J47" t="n">
+      <c r="K47" t="n">
         <v>355973.049</v>
       </c>
     </row>
@@ -1996,9 +2146,12 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
         <v>353779.166</v>
       </c>
-      <c r="J48" t="n">
+      <c r="K48" t="n">
         <v>355973.049</v>
       </c>
     </row>
@@ -2028,9 +2181,12 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
         <v>353782.166</v>
       </c>
-      <c r="J49" t="n">
+      <c r="K49" t="n">
         <v>355973.049</v>
       </c>
     </row>
@@ -2060,9 +2216,12 @@
         <v>0</v>
       </c>
       <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
         <v>353785.166</v>
       </c>
-      <c r="J50" t="n">
+      <c r="K50" t="n">
         <v>355973.049</v>
       </c>
     </row>
@@ -2092,9 +2251,12 @@
         <v>0</v>
       </c>
       <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
         <v>353788.166</v>
       </c>
-      <c r="J51" t="n">
+      <c r="K51" t="n">
         <v>355973.049</v>
       </c>
     </row>
@@ -2124,9 +2286,12 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
         <v>353791.166</v>
       </c>
-      <c r="J52" t="n">
+      <c r="K52" t="n">
         <v>355973.049</v>
       </c>
     </row>
@@ -2156,9 +2321,12 @@
         <v>0</v>
       </c>
       <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
         <v>353794.166</v>
       </c>
-      <c r="J53" t="n">
+      <c r="K53" t="n">
         <v>355973.049</v>
       </c>
     </row>
@@ -2188,9 +2356,12 @@
         <v>0</v>
       </c>
       <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
         <v>353797.166</v>
       </c>
-      <c r="J54" t="n">
+      <c r="K54" t="n">
         <v>355973.049</v>
       </c>
     </row>
@@ -2220,9 +2391,12 @@
         <v>0</v>
       </c>
       <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
         <v>353743.166</v>
       </c>
-      <c r="J55" t="n">
+      <c r="K55" t="n">
         <v>355970.049</v>
       </c>
     </row>
@@ -2231,7 +2405,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>1112.544</v>
+        <v>1112.836</v>
       </c>
       <c r="C56" s="2" t="n">
         <v>1111.02</v>
@@ -2240,7 +2414,7 @@
         <v>1113.17</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>1114.38</v>
+        <v>1115.55</v>
       </c>
       <c r="F56" s="2" t="n">
         <v>1111.6</v>
@@ -2252,9 +2426,12 @@
         <v>1</v>
       </c>
       <c r="I56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="2" t="n">
         <v>353746.166</v>
       </c>
-      <c r="J56" s="2" t="n">
+      <c r="K56" s="2" t="n">
         <v>355970.049</v>
       </c>
     </row>
@@ -2263,7 +2440,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>1114.79</v>
+        <v>1115.045</v>
       </c>
       <c r="C57" s="2" t="n">
         <v>1113.17</v>
@@ -2272,10 +2449,10 @@
         <v>1115.91</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>1115.7</v>
+        <v>1115.55</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>1114.38</v>
+        <v>1115.55</v>
       </c>
       <c r="G57" s="2" t="n">
         <v>6.56</v>
@@ -2284,9 +2461,12 @@
         <v>2</v>
       </c>
       <c r="I57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="2" t="n">
         <v>353749.166</v>
       </c>
-      <c r="J57" s="2" t="n">
+      <c r="K57" s="2" t="n">
         <v>355970.049</v>
       </c>
     </row>
@@ -2295,7 +2475,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>1115.868</v>
+        <v>1115.682</v>
       </c>
       <c r="C58" s="2" t="n">
         <v>1115.91</v>
@@ -2304,10 +2484,10 @@
         <v>1115.72</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>1116.15</v>
+        <v>1115.55</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>1115.7</v>
+        <v>1115.55</v>
       </c>
       <c r="G58" s="2" t="n">
         <v>9</v>
@@ -2316,9 +2496,12 @@
         <v>2</v>
       </c>
       <c r="I58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="2" t="n">
         <v>353752.166</v>
       </c>
-      <c r="J58" s="2" t="n">
+      <c r="K58" s="2" t="n">
         <v>355970.049</v>
       </c>
     </row>
@@ -2327,19 +2510,19 @@
         <v>58</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>1116.016</v>
+        <v>1115.592</v>
       </c>
       <c r="C59" s="2" t="n">
         <v>1115.72</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>1115.77</v>
+        <v>1115.55</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>1116.43</v>
+        <v>1115.55</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>1116.15</v>
+        <v>1115.55</v>
       </c>
       <c r="G59" s="2" t="n">
         <v>9</v>
@@ -2348,9 +2531,12 @@
         <v>3</v>
       </c>
       <c r="I59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="2" t="n">
         <v>353755.166</v>
       </c>
-      <c r="J59" s="2" t="n">
+      <c r="K59" s="2" t="n">
         <v>355970.049</v>
       </c>
     </row>
@@ -2359,19 +2545,19 @@
         <v>59</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>1116.289</v>
+        <v>1115.55</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>1115.77</v>
+        <v>1115.55</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>1116.4</v>
+        <v>1115.55</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>1116.55</v>
+        <v>1115.55</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>1116.43</v>
+        <v>1115.55</v>
       </c>
       <c r="G60" s="2" t="n">
         <v>9</v>
@@ -2380,9 +2566,12 @@
         <v>4</v>
       </c>
       <c r="I60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="2" t="n">
         <v>353758.166</v>
       </c>
-      <c r="J60" s="2" t="n">
+      <c r="K60" s="2" t="n">
         <v>355970.049</v>
       </c>
     </row>
@@ -2391,19 +2580,19 @@
         <v>60</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>1116.923</v>
+        <v>1115.945</v>
       </c>
       <c r="C61" s="2" t="n">
-        <v>1116.4</v>
+        <v>1115.55</v>
       </c>
       <c r="D61" s="2" t="n">
         <v>1117.13</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>1117.6</v>
+        <v>1115.55</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>1116.55</v>
+        <v>1115.55</v>
       </c>
       <c r="G61" s="2" t="n">
         <v>9</v>
@@ -2412,9 +2601,12 @@
         <v>3</v>
       </c>
       <c r="I61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="2" t="n">
         <v>353761.166</v>
       </c>
-      <c r="J61" s="2" t="n">
+      <c r="K61" s="2" t="n">
         <v>355970.049</v>
       </c>
     </row>
@@ -2423,7 +2615,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>1117.513</v>
+        <v>1116.999</v>
       </c>
       <c r="C62" s="2" t="n">
         <v>1117.13</v>
@@ -2435,7 +2627,7 @@
         <v>1117.89</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>1117.6</v>
+        <v>1115.55</v>
       </c>
       <c r="G62" s="2" t="n">
         <v>9</v>
@@ -2444,9 +2636,12 @@
         <v>1</v>
       </c>
       <c r="I62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="2" t="n">
         <v>353764.166</v>
       </c>
-      <c r="J62" s="2" t="n">
+      <c r="K62" s="2" t="n">
         <v>355970.049</v>
       </c>
     </row>
@@ -2476,9 +2671,12 @@
         <v>0</v>
       </c>
       <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
         <v>353767.166</v>
       </c>
-      <c r="J63" t="n">
+      <c r="K63" t="n">
         <v>355970.049</v>
       </c>
     </row>
@@ -2508,9 +2706,12 @@
         <v>0</v>
       </c>
       <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
         <v>353770.166</v>
       </c>
-      <c r="J64" t="n">
+      <c r="K64" t="n">
         <v>355970.049</v>
       </c>
     </row>
@@ -2540,9 +2741,12 @@
         <v>0</v>
       </c>
       <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
         <v>353773.166</v>
       </c>
-      <c r="J65" t="n">
+      <c r="K65" t="n">
         <v>355970.049</v>
       </c>
     </row>
@@ -2572,9 +2776,12 @@
         <v>0</v>
       </c>
       <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
         <v>353776.166</v>
       </c>
-      <c r="J66" t="n">
+      <c r="K66" t="n">
         <v>355970.049</v>
       </c>
     </row>
@@ -2604,9 +2811,12 @@
         <v>0</v>
       </c>
       <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
         <v>353779.166</v>
       </c>
-      <c r="J67" t="n">
+      <c r="K67" t="n">
         <v>355970.049</v>
       </c>
     </row>
@@ -2636,9 +2846,12 @@
         <v>0</v>
       </c>
       <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
         <v>353782.166</v>
       </c>
-      <c r="J68" t="n">
+      <c r="K68" t="n">
         <v>355970.049</v>
       </c>
     </row>
@@ -2668,9 +2881,12 @@
         <v>0</v>
       </c>
       <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
         <v>353785.166</v>
       </c>
-      <c r="J69" t="n">
+      <c r="K69" t="n">
         <v>355970.049</v>
       </c>
     </row>
@@ -2700,9 +2916,12 @@
         <v>0</v>
       </c>
       <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
         <v>353788.166</v>
       </c>
-      <c r="J70" t="n">
+      <c r="K70" t="n">
         <v>355970.049</v>
       </c>
     </row>
@@ -2732,9 +2951,12 @@
         <v>0</v>
       </c>
       <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
         <v>353791.166</v>
       </c>
-      <c r="J71" t="n">
+      <c r="K71" t="n">
         <v>355970.049</v>
       </c>
     </row>
@@ -2764,9 +2986,12 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="n">
         <v>353794.166</v>
       </c>
-      <c r="J72" t="n">
+      <c r="K72" t="n">
         <v>355970.049</v>
       </c>
     </row>
@@ -2796,9 +3021,12 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
         <v>353797.166</v>
       </c>
-      <c r="J73" t="n">
+      <c r="K73" t="n">
         <v>355970.049</v>
       </c>
     </row>
@@ -2828,9 +3056,12 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="n">
         <v>353737.166</v>
       </c>
-      <c r="J74" t="n">
+      <c r="K74" t="n">
         <v>355967.049</v>
       </c>
     </row>
@@ -2839,7 +3070,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>1112.799</v>
+        <v>1113.367</v>
       </c>
       <c r="C75" s="2" t="n">
         <v>1112.02</v>
@@ -2848,7 +3079,7 @@
         <v>1113.64</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>1113.28</v>
+        <v>1115.55</v>
       </c>
       <c r="F75" s="2" t="n">
         <v>1112.26</v>
@@ -2860,9 +3091,12 @@
         <v>1</v>
       </c>
       <c r="I75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="2" t="n">
         <v>353740.166</v>
       </c>
-      <c r="J75" s="2" t="n">
+      <c r="K75" s="2" t="n">
         <v>355967.049</v>
       </c>
     </row>
@@ -2871,7 +3105,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>1112.939</v>
+        <v>1114.085</v>
       </c>
       <c r="C76" s="2" t="n">
         <v>1113.64</v>
@@ -2880,10 +3114,10 @@
         <v>1111.6</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>1113.24</v>
+        <v>1115.55</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>1113.28</v>
+        <v>1115.55</v>
       </c>
       <c r="G76" s="2" t="n">
         <v>8.85</v>
@@ -2892,9 +3126,12 @@
         <v>2</v>
       </c>
       <c r="I76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" s="2" t="n">
         <v>353743.166</v>
       </c>
-      <c r="J76" s="2" t="n">
+      <c r="K76" s="2" t="n">
         <v>355967.049</v>
       </c>
     </row>
@@ -2903,19 +3140,19 @@
         <v>76</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>1113.56</v>
+        <v>1114.562</v>
       </c>
       <c r="C77" s="2" t="n">
         <v>1111.6</v>
       </c>
       <c r="D77" s="2" t="n">
-        <v>1114.38</v>
+        <v>1115.55</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>1115.02</v>
+        <v>1115.55</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>1113.24</v>
+        <v>1115.55</v>
       </c>
       <c r="G77" s="2" t="n">
         <v>9</v>
@@ -2924,9 +3161,12 @@
         <v>3</v>
       </c>
       <c r="I77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="2" t="n">
         <v>353746.166</v>
       </c>
-      <c r="J77" s="2" t="n">
+      <c r="K77" s="2" t="n">
         <v>355967.049</v>
       </c>
     </row>
@@ -2935,19 +3175,19 @@
         <v>77</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>1115.203</v>
+        <v>1115.55</v>
       </c>
       <c r="C78" s="2" t="n">
-        <v>1114.38</v>
+        <v>1115.55</v>
       </c>
       <c r="D78" s="2" t="n">
-        <v>1115.7</v>
+        <v>1115.55</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>1115.71</v>
+        <v>1115.55</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>1115.02</v>
+        <v>1115.55</v>
       </c>
       <c r="G78" s="2" t="n">
         <v>9</v>
@@ -2956,9 +3196,12 @@
         <v>4</v>
       </c>
       <c r="I78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="2" t="n">
         <v>353749.166</v>
       </c>
-      <c r="J78" s="2" t="n">
+      <c r="K78" s="2" t="n">
         <v>355967.049</v>
       </c>
     </row>
@@ -2967,19 +3210,19 @@
         <v>78</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>1115.942</v>
+        <v>1115.55</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>1115.7</v>
+        <v>1115.55</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>1116.15</v>
+        <v>1115.55</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>1116.22</v>
+        <v>1115.55</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>1115.71</v>
+        <v>1115.55</v>
       </c>
       <c r="G79" s="2" t="n">
         <v>9</v>
@@ -2988,9 +3231,12 @@
         <v>4</v>
       </c>
       <c r="I79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="2" t="n">
         <v>353752.166</v>
       </c>
-      <c r="J79" s="2" t="n">
+      <c r="K79" s="2" t="n">
         <v>355967.049</v>
       </c>
     </row>
@@ -2999,19 +3245,19 @@
         <v>79</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>1116.366</v>
+        <v>1115.55</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>1116.15</v>
+        <v>1115.55</v>
       </c>
       <c r="D80" s="2" t="n">
-        <v>1116.43</v>
+        <v>1115.55</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>1116.67</v>
+        <v>1115.55</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>1116.22</v>
+        <v>1115.55</v>
       </c>
       <c r="G80" s="2" t="n">
         <v>9</v>
@@ -3020,9 +3266,12 @@
         <v>4</v>
       </c>
       <c r="I80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="2" t="n">
         <v>353755.166</v>
       </c>
-      <c r="J80" s="2" t="n">
+      <c r="K80" s="2" t="n">
         <v>355967.049</v>
       </c>
     </row>
@@ -3031,19 +3280,19 @@
         <v>80</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>1116.698</v>
+        <v>1115.55</v>
       </c>
       <c r="C81" s="2" t="n">
-        <v>1116.43</v>
+        <v>1115.55</v>
       </c>
       <c r="D81" s="2" t="n">
-        <v>1116.55</v>
+        <v>1115.55</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>1117.14</v>
+        <v>1115.55</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>1116.67</v>
+        <v>1115.55</v>
       </c>
       <c r="G81" s="2" t="n">
         <v>9</v>
@@ -3052,9 +3301,12 @@
         <v>4</v>
       </c>
       <c r="I81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="2" t="n">
         <v>353758.166</v>
       </c>
-      <c r="J81" s="2" t="n">
+      <c r="K81" s="2" t="n">
         <v>355967.049</v>
       </c>
     </row>
@@ -3063,19 +3315,19 @@
         <v>81</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>1117.159</v>
+        <v>1115.55</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>1116.55</v>
+        <v>1115.55</v>
       </c>
       <c r="D82" s="2" t="n">
-        <v>1117.6</v>
+        <v>1115.55</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>1117.34</v>
+        <v>1115.55</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>1117.14</v>
+        <v>1115.55</v>
       </c>
       <c r="G82" s="2" t="n">
         <v>9</v>
@@ -3084,9 +3336,12 @@
         <v>4</v>
       </c>
       <c r="I82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="2" t="n">
         <v>353761.166</v>
       </c>
-      <c r="J82" s="2" t="n">
+      <c r="K82" s="2" t="n">
         <v>355967.049</v>
       </c>
     </row>
@@ -3095,10 +3350,10 @@
         <v>82</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>1117.91</v>
+        <v>1116.949</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>1117.6</v>
+        <v>1115.55</v>
       </c>
       <c r="D83" s="2" t="n">
         <v>1117.89</v>
@@ -3107,7 +3362,7 @@
         <v>1118.81</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>1117.34</v>
+        <v>1115.55</v>
       </c>
       <c r="G83" s="2" t="n">
         <v>9</v>
@@ -3116,9 +3371,12 @@
         <v>2</v>
       </c>
       <c r="I83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="2" t="n">
         <v>353764.166</v>
       </c>
-      <c r="J83" s="2" t="n">
+      <c r="K83" s="2" t="n">
         <v>355967.049</v>
       </c>
     </row>
@@ -3148,9 +3406,12 @@
         <v>0</v>
       </c>
       <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="n">
         <v>353767.166</v>
       </c>
-      <c r="J84" t="n">
+      <c r="K84" t="n">
         <v>355967.049</v>
       </c>
     </row>
@@ -3180,9 +3441,12 @@
         <v>0</v>
       </c>
       <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="n">
         <v>353770.166</v>
       </c>
-      <c r="J85" t="n">
+      <c r="K85" t="n">
         <v>355967.049</v>
       </c>
     </row>
@@ -3212,9 +3476,12 @@
         <v>0</v>
       </c>
       <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="n">
         <v>353773.166</v>
       </c>
-      <c r="J86" t="n">
+      <c r="K86" t="n">
         <v>355967.049</v>
       </c>
     </row>
@@ -3244,9 +3511,12 @@
         <v>0</v>
       </c>
       <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="n">
         <v>353776.166</v>
       </c>
-      <c r="J87" t="n">
+      <c r="K87" t="n">
         <v>355967.049</v>
       </c>
     </row>
@@ -3276,9 +3546,12 @@
         <v>0</v>
       </c>
       <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="n">
         <v>353779.166</v>
       </c>
-      <c r="J88" t="n">
+      <c r="K88" t="n">
         <v>355967.049</v>
       </c>
     </row>
@@ -3308,9 +3581,12 @@
         <v>0</v>
       </c>
       <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="n">
         <v>353782.166</v>
       </c>
-      <c r="J89" t="n">
+      <c r="K89" t="n">
         <v>355967.049</v>
       </c>
     </row>
@@ -3340,9 +3616,12 @@
         <v>0</v>
       </c>
       <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="n">
         <v>353785.166</v>
       </c>
-      <c r="J90" t="n">
+      <c r="K90" t="n">
         <v>355967.049</v>
       </c>
     </row>
@@ -3372,9 +3651,12 @@
         <v>0</v>
       </c>
       <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="n">
         <v>353788.166</v>
       </c>
-      <c r="J91" t="n">
+      <c r="K91" t="n">
         <v>355967.049</v>
       </c>
     </row>
@@ -3404,9 +3686,12 @@
         <v>0</v>
       </c>
       <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="n">
         <v>353791.166</v>
       </c>
-      <c r="J92" t="n">
+      <c r="K92" t="n">
         <v>355967.049</v>
       </c>
     </row>
@@ -3436,9 +3721,12 @@
         <v>0</v>
       </c>
       <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="n">
         <v>353794.166</v>
       </c>
-      <c r="J93" t="n">
+      <c r="K93" t="n">
         <v>355967.049</v>
       </c>
     </row>
@@ -3468,9 +3756,12 @@
         <v>0</v>
       </c>
       <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
         <v>353797.166</v>
       </c>
-      <c r="J94" t="n">
+      <c r="K94" t="n">
         <v>355967.049</v>
       </c>
     </row>
@@ -3479,16 +3770,16 @@
         <v>94</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>1112.858</v>
+        <v>1113.98</v>
       </c>
       <c r="C95" s="2" t="n">
         <v>1112.26</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>1113.28</v>
+        <v>1115.55</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>1113.33</v>
+        <v>1115.55</v>
       </c>
       <c r="F95" s="2" t="n">
         <v>1112.56</v>
@@ -3500,9 +3791,12 @@
         <v>2</v>
       </c>
       <c r="I95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="2" t="n">
         <v>353740.166</v>
       </c>
-      <c r="J95" s="2" t="n">
+      <c r="K95" s="2" t="n">
         <v>355964.049</v>
       </c>
     </row>
@@ -3511,19 +3805,19 @@
         <v>95</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>1113.45</v>
+        <v>1115.55</v>
       </c>
       <c r="C96" s="2" t="n">
-        <v>1113.28</v>
+        <v>1115.55</v>
       </c>
       <c r="D96" s="2" t="n">
-        <v>1113.24</v>
+        <v>1115.55</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>1113.95</v>
+        <v>1115.55</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>1113.33</v>
+        <v>1115.55</v>
       </c>
       <c r="G96" s="2" t="n">
         <v>9</v>
@@ -3532,9 +3826,12 @@
         <v>4</v>
       </c>
       <c r="I96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" s="2" t="n">
         <v>353743.166</v>
       </c>
-      <c r="J96" s="2" t="n">
+      <c r="K96" s="2" t="n">
         <v>355964.049</v>
       </c>
     </row>
@@ -3543,19 +3840,19 @@
         <v>96</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>1114.356</v>
+        <v>1115.55</v>
       </c>
       <c r="C97" s="2" t="n">
-        <v>1113.24</v>
+        <v>1115.55</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>1115.02</v>
+        <v>1115.55</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>1115.22</v>
+        <v>1115.55</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>1113.95</v>
+        <v>1115.55</v>
       </c>
       <c r="G97" s="2" t="n">
         <v>9</v>
@@ -3564,9 +3861,12 @@
         <v>4</v>
       </c>
       <c r="I97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="2" t="n">
         <v>353746.166</v>
       </c>
-      <c r="J97" s="2" t="n">
+      <c r="K97" s="2" t="n">
         <v>355964.049</v>
       </c>
     </row>
@@ -3575,19 +3875,19 @@
         <v>97</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>1115.418</v>
+        <v>1115.55</v>
       </c>
       <c r="C98" s="2" t="n">
-        <v>1115.02</v>
+        <v>1115.55</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>1115.71</v>
+        <v>1115.55</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>1115.72</v>
+        <v>1115.55</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>1115.22</v>
+        <v>1115.55</v>
       </c>
       <c r="G98" s="2" t="n">
         <v>9</v>
@@ -3596,9 +3896,12 @@
         <v>4</v>
       </c>
       <c r="I98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="2" t="n">
         <v>353749.166</v>
       </c>
-      <c r="J98" s="2" t="n">
+      <c r="K98" s="2" t="n">
         <v>355964.049</v>
       </c>
     </row>
@@ -3607,19 +3910,19 @@
         <v>98</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>1115.97</v>
+        <v>1115.55</v>
       </c>
       <c r="C99" s="2" t="n">
-        <v>1115.71</v>
+        <v>1115.55</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>1116.22</v>
+        <v>1115.55</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>1116.23</v>
+        <v>1115.55</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>1115.72</v>
+        <v>1115.55</v>
       </c>
       <c r="G99" s="2" t="n">
         <v>9</v>
@@ -3628,9 +3931,12 @@
         <v>4</v>
       </c>
       <c r="I99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" s="2" t="n">
         <v>353752.166</v>
       </c>
-      <c r="J99" s="2" t="n">
+      <c r="K99" s="2" t="n">
         <v>355964.049</v>
       </c>
     </row>
@@ -3639,19 +3945,19 @@
         <v>99</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>1116.465</v>
+        <v>1115.55</v>
       </c>
       <c r="C100" s="2" t="n">
-        <v>1116.22</v>
+        <v>1115.55</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>1116.67</v>
+        <v>1115.55</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>1116.74</v>
+        <v>1115.55</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>1116.23</v>
+        <v>1115.55</v>
       </c>
       <c r="G100" s="2" t="n">
         <v>9</v>
@@ -3660,9 +3966,12 @@
         <v>4</v>
       </c>
       <c r="I100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="2" t="n">
         <v>353755.166</v>
       </c>
-      <c r="J100" s="2" t="n">
+      <c r="K100" s="2" t="n">
         <v>355964.049</v>
       </c>
     </row>
@@ -3671,19 +3980,19 @@
         <v>100</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>1116.938</v>
+        <v>1115.55</v>
       </c>
       <c r="C101" s="2" t="n">
-        <v>1116.67</v>
+        <v>1115.55</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>1117.14</v>
+        <v>1115.55</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>1117.21</v>
+        <v>1115.55</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>1116.74</v>
+        <v>1115.55</v>
       </c>
       <c r="G101" s="2" t="n">
         <v>9</v>
@@ -3692,9 +4001,12 @@
         <v>4</v>
       </c>
       <c r="I101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" s="2" t="n">
         <v>353758.166</v>
       </c>
-      <c r="J101" s="2" t="n">
+      <c r="K101" s="2" t="n">
         <v>355964.049</v>
       </c>
     </row>
@@ -3703,19 +4015,19 @@
         <v>101</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>1117.331</v>
+        <v>1115.55</v>
       </c>
       <c r="C102" s="2" t="n">
-        <v>1117.14</v>
+        <v>1115.55</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>1117.34</v>
+        <v>1115.55</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>1117.64</v>
+        <v>1115.55</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>1117.21</v>
+        <v>1115.55</v>
       </c>
       <c r="G102" s="2" t="n">
         <v>9</v>
@@ -3724,9 +4036,12 @@
         <v>4</v>
       </c>
       <c r="I102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" s="2" t="n">
         <v>353761.166</v>
       </c>
-      <c r="J102" s="2" t="n">
+      <c r="K102" s="2" t="n">
         <v>355964.049</v>
       </c>
     </row>
@@ -3735,10 +4050,10 @@
         <v>102</v>
       </c>
       <c r="B103" s="2" t="n">
-        <v>1117.978</v>
+        <v>1117.007</v>
       </c>
       <c r="C103" s="2" t="n">
-        <v>1117.34</v>
+        <v>1115.55</v>
       </c>
       <c r="D103" s="2" t="n">
         <v>1118.81</v>
@@ -3747,7 +4062,7 @@
         <v>1118.12</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>1117.64</v>
+        <v>1115.55</v>
       </c>
       <c r="G103" s="2" t="n">
         <v>9</v>
@@ -3756,9 +4071,12 @@
         <v>2</v>
       </c>
       <c r="I103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" s="2" t="n">
         <v>353764.166</v>
       </c>
-      <c r="J103" s="2" t="n">
+      <c r="K103" s="2" t="n">
         <v>355964.049</v>
       </c>
     </row>
@@ -3788,9 +4106,12 @@
         <v>0</v>
       </c>
       <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="n">
         <v>353767.166</v>
       </c>
-      <c r="J104" t="n">
+      <c r="K104" t="n">
         <v>355964.049</v>
       </c>
     </row>
@@ -3820,9 +4141,12 @@
         <v>0</v>
       </c>
       <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="n">
         <v>353770.166</v>
       </c>
-      <c r="J105" t="n">
+      <c r="K105" t="n">
         <v>355964.049</v>
       </c>
     </row>
@@ -3852,9 +4176,12 @@
         <v>0</v>
       </c>
       <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="n">
         <v>353773.166</v>
       </c>
-      <c r="J106" t="n">
+      <c r="K106" t="n">
         <v>355964.049</v>
       </c>
     </row>
@@ -3884,9 +4211,12 @@
         <v>0</v>
       </c>
       <c r="I107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" t="n">
         <v>353776.166</v>
       </c>
-      <c r="J107" t="n">
+      <c r="K107" t="n">
         <v>355964.049</v>
       </c>
     </row>
@@ -3916,9 +4246,12 @@
         <v>0</v>
       </c>
       <c r="I108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" t="n">
         <v>353779.166</v>
       </c>
-      <c r="J108" t="n">
+      <c r="K108" t="n">
         <v>355964.049</v>
       </c>
     </row>
@@ -3948,9 +4281,12 @@
         <v>0</v>
       </c>
       <c r="I109" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" t="n">
         <v>353782.166</v>
       </c>
-      <c r="J109" t="n">
+      <c r="K109" t="n">
         <v>355964.049</v>
       </c>
     </row>
@@ -3980,9 +4316,12 @@
         <v>0</v>
       </c>
       <c r="I110" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" t="n">
         <v>353785.166</v>
       </c>
-      <c r="J110" t="n">
+      <c r="K110" t="n">
         <v>355964.049</v>
       </c>
     </row>
@@ -4012,9 +4351,12 @@
         <v>0</v>
       </c>
       <c r="I111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" t="n">
         <v>353788.166</v>
       </c>
-      <c r="J111" t="n">
+      <c r="K111" t="n">
         <v>355964.049</v>
       </c>
     </row>
@@ -4044,9 +4386,12 @@
         <v>0</v>
       </c>
       <c r="I112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" t="n">
         <v>353791.166</v>
       </c>
-      <c r="J112" t="n">
+      <c r="K112" t="n">
         <v>355964.049</v>
       </c>
     </row>
@@ -4076,9 +4421,12 @@
         <v>0</v>
       </c>
       <c r="I113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" t="n">
         <v>353794.166</v>
       </c>
-      <c r="J113" t="n">
+      <c r="K113" t="n">
         <v>355964.049</v>
       </c>
     </row>
@@ -4108,9 +4456,12 @@
         <v>0</v>
       </c>
       <c r="I114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" t="n">
         <v>353797.166</v>
       </c>
-      <c r="J114" t="n">
+      <c r="K114" t="n">
         <v>355964.049</v>
       </c>
     </row>
@@ -4119,13 +4470,13 @@
         <v>114</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>1113.038</v>
+        <v>1113.592</v>
       </c>
       <c r="C115" s="2" t="n">
         <v>1112.56</v>
       </c>
       <c r="D115" s="2" t="n">
-        <v>1113.33</v>
+        <v>1115.55</v>
       </c>
       <c r="E115" s="2" t="n">
         <v>1113.39</v>
@@ -4140,9 +4491,12 @@
         <v>1</v>
       </c>
       <c r="I115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" s="2" t="n">
         <v>353740.166</v>
       </c>
-      <c r="J115" s="2" t="n">
+      <c r="K115" s="2" t="n">
         <v>355961.049</v>
       </c>
     </row>
@@ -4151,16 +4505,16 @@
         <v>115</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>1113.849</v>
+        <v>1115.01</v>
       </c>
       <c r="C116" s="2" t="n">
-        <v>1113.33</v>
+        <v>1115.55</v>
       </c>
       <c r="D116" s="2" t="n">
-        <v>1113.95</v>
+        <v>1115.55</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>1114.72</v>
+        <v>1115.55</v>
       </c>
       <c r="F116" s="2" t="n">
         <v>1113.39</v>
@@ -4172,9 +4526,12 @@
         <v>3</v>
       </c>
       <c r="I116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" s="2" t="n">
         <v>353743.166</v>
       </c>
-      <c r="J116" s="2" t="n">
+      <c r="K116" s="2" t="n">
         <v>355961.049</v>
       </c>
     </row>
@@ -4183,19 +4540,19 @@
         <v>116</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>1114.779</v>
+        <v>1115.55</v>
       </c>
       <c r="C117" s="2" t="n">
-        <v>1113.95</v>
+        <v>1115.55</v>
       </c>
       <c r="D117" s="2" t="n">
-        <v>1115.22</v>
+        <v>1115.55</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>1115.23</v>
+        <v>1115.55</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>1114.72</v>
+        <v>1115.55</v>
       </c>
       <c r="G117" s="2" t="n">
         <v>9</v>
@@ -4204,9 +4561,12 @@
         <v>4</v>
       </c>
       <c r="I117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" s="2" t="n">
         <v>353746.166</v>
       </c>
-      <c r="J117" s="2" t="n">
+      <c r="K117" s="2" t="n">
         <v>355961.049</v>
       </c>
     </row>
@@ -4215,19 +4575,19 @@
         <v>117</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>1115.477</v>
+        <v>1115.55</v>
       </c>
       <c r="C118" s="2" t="n">
-        <v>1115.22</v>
+        <v>1115.55</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>1115.72</v>
+        <v>1115.55</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>1115.74</v>
+        <v>1115.55</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>1115.23</v>
+        <v>1115.55</v>
       </c>
       <c r="G118" s="2" t="n">
         <v>9</v>
@@ -4236,9 +4596,12 @@
         <v>4</v>
       </c>
       <c r="I118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" s="2" t="n">
         <v>353749.166</v>
       </c>
-      <c r="J118" s="2" t="n">
+      <c r="K118" s="2" t="n">
         <v>355961.049</v>
       </c>
     </row>
@@ -4247,19 +4610,19 @@
         <v>118</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>1115.984</v>
+        <v>1115.55</v>
       </c>
       <c r="C119" s="2" t="n">
-        <v>1115.72</v>
+        <v>1115.55</v>
       </c>
       <c r="D119" s="2" t="n">
-        <v>1116.23</v>
+        <v>1115.55</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>1116.25</v>
+        <v>1115.55</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>1115.74</v>
+        <v>1115.55</v>
       </c>
       <c r="G119" s="2" t="n">
         <v>9</v>
@@ -4268,9 +4631,12 @@
         <v>4</v>
       </c>
       <c r="I119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" s="2" t="n">
         <v>353752.166</v>
       </c>
-      <c r="J119" s="2" t="n">
+      <c r="K119" s="2" t="n">
         <v>355961.049</v>
       </c>
     </row>
@@ -4279,19 +4645,19 @@
         <v>119</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>1116.492</v>
+        <v>1115.55</v>
       </c>
       <c r="C120" s="2" t="n">
-        <v>1116.23</v>
+        <v>1115.55</v>
       </c>
       <c r="D120" s="2" t="n">
-        <v>1116.74</v>
+        <v>1115.55</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>1116.75</v>
+        <v>1115.55</v>
       </c>
       <c r="F120" s="2" t="n">
-        <v>1116.25</v>
+        <v>1115.55</v>
       </c>
       <c r="G120" s="2" t="n">
         <v>9</v>
@@ -4300,9 +4666,12 @@
         <v>4</v>
       </c>
       <c r="I120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" s="2" t="n">
         <v>353755.166</v>
       </c>
-      <c r="J120" s="2" t="n">
+      <c r="K120" s="2" t="n">
         <v>355961.049</v>
       </c>
     </row>
@@ -4311,19 +4680,19 @@
         <v>120</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>1116.99</v>
+        <v>1115.55</v>
       </c>
       <c r="C121" s="2" t="n">
-        <v>1116.74</v>
+        <v>1115.55</v>
       </c>
       <c r="D121" s="2" t="n">
-        <v>1117.21</v>
+        <v>1115.55</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>1117.26</v>
+        <v>1115.55</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>1116.75</v>
+        <v>1115.55</v>
       </c>
       <c r="G121" s="2" t="n">
         <v>9</v>
@@ -4332,9 +4701,12 @@
         <v>4</v>
       </c>
       <c r="I121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" s="2" t="n">
         <v>353758.166</v>
       </c>
-      <c r="J121" s="2" t="n">
+      <c r="K121" s="2" t="n">
         <v>355961.049</v>
       </c>
     </row>
@@ -4343,19 +4715,19 @@
         <v>121</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>1117.463</v>
+        <v>1115.55</v>
       </c>
       <c r="C122" s="2" t="n">
-        <v>1117.21</v>
+        <v>1115.55</v>
       </c>
       <c r="D122" s="2" t="n">
-        <v>1117.64</v>
+        <v>1115.55</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>1117.74</v>
+        <v>1115.55</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>1117.26</v>
+        <v>1115.55</v>
       </c>
       <c r="G122" s="2" t="n">
         <v>9</v>
@@ -4364,9 +4736,12 @@
         <v>4</v>
       </c>
       <c r="I122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" s="2" t="n">
         <v>353761.166</v>
       </c>
-      <c r="J122" s="2" t="n">
+      <c r="K122" s="2" t="n">
         <v>355961.049</v>
       </c>
     </row>
@@ -4375,10 +4750,10 @@
         <v>122</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>1117.911</v>
+        <v>1116.84</v>
       </c>
       <c r="C123" s="2" t="n">
-        <v>1117.64</v>
+        <v>1115.55</v>
       </c>
       <c r="D123" s="2" t="n">
         <v>1118.12</v>
@@ -4387,7 +4762,7 @@
         <v>1118.14</v>
       </c>
       <c r="F123" s="2" t="n">
-        <v>1117.74</v>
+        <v>1115.55</v>
       </c>
       <c r="G123" s="2" t="n">
         <v>9</v>
@@ -4396,9 +4771,12 @@
         <v>2</v>
       </c>
       <c r="I123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" s="2" t="n">
         <v>353764.166</v>
       </c>
-      <c r="J123" s="2" t="n">
+      <c r="K123" s="2" t="n">
         <v>355961.049</v>
       </c>
     </row>
@@ -4428,9 +4806,12 @@
         <v>0</v>
       </c>
       <c r="I124" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" t="n">
         <v>353767.166</v>
       </c>
-      <c r="J124" t="n">
+      <c r="K124" t="n">
         <v>355961.049</v>
       </c>
     </row>
@@ -4460,9 +4841,12 @@
         <v>0</v>
       </c>
       <c r="I125" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" t="n">
         <v>353770.166</v>
       </c>
-      <c r="J125" t="n">
+      <c r="K125" t="n">
         <v>355961.049</v>
       </c>
     </row>
@@ -4492,9 +4876,12 @@
         <v>0</v>
       </c>
       <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="n">
         <v>353773.166</v>
       </c>
-      <c r="J126" t="n">
+      <c r="K126" t="n">
         <v>355961.049</v>
       </c>
     </row>
@@ -4524,9 +4911,12 @@
         <v>0</v>
       </c>
       <c r="I127" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" t="n">
         <v>353776.166</v>
       </c>
-      <c r="J127" t="n">
+      <c r="K127" t="n">
         <v>355961.049</v>
       </c>
     </row>
@@ -4556,9 +4946,12 @@
         <v>0</v>
       </c>
       <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="n">
         <v>353779.166</v>
       </c>
-      <c r="J128" t="n">
+      <c r="K128" t="n">
         <v>355961.049</v>
       </c>
     </row>
@@ -4588,9 +4981,12 @@
         <v>0</v>
       </c>
       <c r="I129" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" t="n">
         <v>353782.166</v>
       </c>
-      <c r="J129" t="n">
+      <c r="K129" t="n">
         <v>355961.049</v>
       </c>
     </row>
@@ -4620,9 +5016,12 @@
         <v>0</v>
       </c>
       <c r="I130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" t="n">
         <v>353785.166</v>
       </c>
-      <c r="J130" t="n">
+      <c r="K130" t="n">
         <v>355961.049</v>
       </c>
     </row>
@@ -4652,9 +5051,12 @@
         <v>0</v>
       </c>
       <c r="I131" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" t="n">
         <v>353788.166</v>
       </c>
-      <c r="J131" t="n">
+      <c r="K131" t="n">
         <v>355961.049</v>
       </c>
     </row>
@@ -4684,9 +5086,12 @@
         <v>0</v>
       </c>
       <c r="I132" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" t="n">
         <v>353791.166</v>
       </c>
-      <c r="J132" t="n">
+      <c r="K132" t="n">
         <v>355961.049</v>
       </c>
     </row>
@@ -4716,9 +5121,12 @@
         <v>0</v>
       </c>
       <c r="I133" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" t="n">
         <v>353794.166</v>
       </c>
-      <c r="J133" t="n">
+      <c r="K133" t="n">
         <v>355961.049</v>
       </c>
     </row>
@@ -4748,9 +5156,12 @@
         <v>0</v>
       </c>
       <c r="I134" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" t="n">
         <v>353797.166</v>
       </c>
-      <c r="J134" t="n">
+      <c r="K134" t="n">
         <v>355961.049</v>
       </c>
     </row>
@@ -4780,9 +5191,12 @@
         <v>0</v>
       </c>
       <c r="I135" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" t="n">
         <v>353740.166</v>
       </c>
-      <c r="J135" t="n">
+      <c r="K135" t="n">
         <v>355958.049</v>
       </c>
     </row>
@@ -4791,16 +5205,16 @@
         <v>135</v>
       </c>
       <c r="B136" s="2" t="n">
-        <v>1114.078</v>
+        <v>1114.489</v>
       </c>
       <c r="C136" s="2" t="n">
         <v>1113.39</v>
       </c>
       <c r="D136" s="2" t="n">
-        <v>1114.72</v>
+        <v>1115.55</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>1114.73</v>
+        <v>1115.55</v>
       </c>
       <c r="F136" s="2" t="n">
         <v>1113.47</v>
@@ -4812,9 +5226,12 @@
         <v>2</v>
       </c>
       <c r="I136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" s="2" t="n">
         <v>353743.166</v>
       </c>
-      <c r="J136" s="2" t="n">
+      <c r="K136" s="2" t="n">
         <v>355958.049</v>
       </c>
     </row>
@@ -4823,19 +5240,19 @@
         <v>136</v>
       </c>
       <c r="B137" s="2" t="n">
-        <v>1114.981</v>
+        <v>1115.55</v>
       </c>
       <c r="C137" s="2" t="n">
-        <v>1114.72</v>
+        <v>1115.55</v>
       </c>
       <c r="D137" s="2" t="n">
-        <v>1115.23</v>
+        <v>1115.55</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>1115.24</v>
+        <v>1115.55</v>
       </c>
       <c r="F137" s="2" t="n">
-        <v>1114.73</v>
+        <v>1115.55</v>
       </c>
       <c r="G137" s="2" t="n">
         <v>9</v>
@@ -4844,9 +5261,12 @@
         <v>4</v>
       </c>
       <c r="I137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" s="2" t="n">
         <v>353746.166</v>
       </c>
-      <c r="J137" s="2" t="n">
+      <c r="K137" s="2" t="n">
         <v>355958.049</v>
       </c>
     </row>
@@ -4855,19 +5275,19 @@
         <v>137</v>
       </c>
       <c r="B138" s="2" t="n">
-        <v>1115.488</v>
+        <v>1115.55</v>
       </c>
       <c r="C138" s="2" t="n">
-        <v>1115.23</v>
+        <v>1115.55</v>
       </c>
       <c r="D138" s="2" t="n">
-        <v>1115.74</v>
+        <v>1115.55</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>1115.75</v>
+        <v>1115.55</v>
       </c>
       <c r="F138" s="2" t="n">
-        <v>1115.24</v>
+        <v>1115.55</v>
       </c>
       <c r="G138" s="2" t="n">
         <v>9</v>
@@ -4876,9 +5296,12 @@
         <v>4</v>
       </c>
       <c r="I138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" s="2" t="n">
         <v>353749.166</v>
       </c>
-      <c r="J138" s="2" t="n">
+      <c r="K138" s="2" t="n">
         <v>355958.049</v>
       </c>
     </row>
@@ -4887,19 +5310,19 @@
         <v>138</v>
       </c>
       <c r="B139" s="2" t="n">
-        <v>1115.996</v>
+        <v>1115.55</v>
       </c>
       <c r="C139" s="2" t="n">
-        <v>1115.74</v>
+        <v>1115.55</v>
       </c>
       <c r="D139" s="2" t="n">
-        <v>1116.25</v>
+        <v>1115.55</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>1116.25</v>
+        <v>1115.55</v>
       </c>
       <c r="F139" s="2" t="n">
-        <v>1115.75</v>
+        <v>1115.55</v>
       </c>
       <c r="G139" s="2" t="n">
         <v>9</v>
@@ -4908,9 +5331,12 @@
         <v>4</v>
       </c>
       <c r="I139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" s="2" t="n">
         <v>353752.166</v>
       </c>
-      <c r="J139" s="2" t="n">
+      <c r="K139" s="2" t="n">
         <v>355958.049</v>
       </c>
     </row>
@@ -4919,19 +5345,19 @@
         <v>139</v>
       </c>
       <c r="B140" s="2" t="n">
-        <v>1116.503</v>
+        <v>1115.55</v>
       </c>
       <c r="C140" s="2" t="n">
-        <v>1116.25</v>
+        <v>1115.55</v>
       </c>
       <c r="D140" s="2" t="n">
-        <v>1116.75</v>
+        <v>1115.55</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>1116.76</v>
+        <v>1115.55</v>
       </c>
       <c r="F140" s="2" t="n">
-        <v>1116.25</v>
+        <v>1115.55</v>
       </c>
       <c r="G140" s="2" t="n">
         <v>9</v>
@@ -4940,9 +5366,12 @@
         <v>4</v>
       </c>
       <c r="I140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" s="2" t="n">
         <v>353755.166</v>
       </c>
-      <c r="J140" s="2" t="n">
+      <c r="K140" s="2" t="n">
         <v>355958.049</v>
       </c>
     </row>
@@ -4951,19 +5380,19 @@
         <v>140</v>
       </c>
       <c r="B141" s="2" t="n">
-        <v>1117.01</v>
+        <v>1115.55</v>
       </c>
       <c r="C141" s="2" t="n">
-        <v>1116.75</v>
+        <v>1115.55</v>
       </c>
       <c r="D141" s="2" t="n">
-        <v>1117.26</v>
+        <v>1115.55</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>1117.27</v>
+        <v>1115.55</v>
       </c>
       <c r="F141" s="2" t="n">
-        <v>1116.76</v>
+        <v>1115.55</v>
       </c>
       <c r="G141" s="2" t="n">
         <v>9</v>
@@ -4972,9 +5401,12 @@
         <v>4</v>
       </c>
       <c r="I141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" s="2" t="n">
         <v>353758.166</v>
       </c>
-      <c r="J141" s="2" t="n">
+      <c r="K141" s="2" t="n">
         <v>355958.049</v>
       </c>
     </row>
@@ -4983,19 +5415,19 @@
         <v>141</v>
       </c>
       <c r="B142" s="2" t="n">
-        <v>1117.511</v>
+        <v>1115.55</v>
       </c>
       <c r="C142" s="2" t="n">
-        <v>1117.26</v>
+        <v>1115.55</v>
       </c>
       <c r="D142" s="2" t="n">
-        <v>1117.74</v>
+        <v>1115.55</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>1117.77</v>
+        <v>1115.55</v>
       </c>
       <c r="F142" s="2" t="n">
-        <v>1117.27</v>
+        <v>1115.55</v>
       </c>
       <c r="G142" s="2" t="n">
         <v>9</v>
@@ -5004,9 +5436,12 @@
         <v>4</v>
       </c>
       <c r="I142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" s="2" t="n">
         <v>353761.166</v>
       </c>
-      <c r="J142" s="2" t="n">
+      <c r="K142" s="2" t="n">
         <v>355958.049</v>
       </c>
     </row>
@@ -5015,10 +5450,10 @@
         <v>142</v>
       </c>
       <c r="B143" s="2" t="n">
-        <v>1117.962</v>
+        <v>1116.858</v>
       </c>
       <c r="C143" s="2" t="n">
-        <v>1117.74</v>
+        <v>1115.55</v>
       </c>
       <c r="D143" s="2" t="n">
         <v>1118.14</v>
@@ -5027,7 +5462,7 @@
         <v>1118.19</v>
       </c>
       <c r="F143" s="2" t="n">
-        <v>1117.77</v>
+        <v>1115.55</v>
       </c>
       <c r="G143" s="2" t="n">
         <v>9</v>
@@ -5036,9 +5471,12 @@
         <v>2</v>
       </c>
       <c r="I143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" s="2" t="n">
         <v>353764.166</v>
       </c>
-      <c r="J143" s="2" t="n">
+      <c r="K143" s="2" t="n">
         <v>355958.049</v>
       </c>
     </row>
@@ -5068,9 +5506,12 @@
         <v>0</v>
       </c>
       <c r="I144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" t="n">
         <v>353767.166</v>
       </c>
-      <c r="J144" t="n">
+      <c r="K144" t="n">
         <v>355958.049</v>
       </c>
     </row>
@@ -5100,73 +5541,82 @@
         <v>0</v>
       </c>
       <c r="I145" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" t="n">
         <v>353770.166</v>
       </c>
-      <c r="J145" t="n">
+      <c r="K145" t="n">
         <v>355958.049</v>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n">
+      <c r="A146" s="3" t="n">
         <v>145</v>
       </c>
-      <c r="B146" s="2" t="n">
+      <c r="B146" s="3" t="n">
         <v>1121.054</v>
       </c>
-      <c r="C146" s="2" t="n">
+      <c r="C146" s="3" t="n">
         <v>1120.58</v>
       </c>
-      <c r="D146" s="2" t="n">
+      <c r="D146" s="3" t="n">
         <v>1120.79</v>
       </c>
-      <c r="E146" s="2" t="n">
+      <c r="E146" s="3" t="n">
         <v>1121.17</v>
       </c>
-      <c r="F146" s="2" t="n">
+      <c r="F146" s="3" t="n">
         <v>1121.67</v>
       </c>
-      <c r="G146" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="H146" s="2" t="n">
+      <c r="G146" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="H146" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I146" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I146" s="2" t="n">
+      <c r="J146" s="3" t="n">
         <v>353773.166</v>
       </c>
-      <c r="J146" s="2" t="n">
+      <c r="K146" s="3" t="n">
         <v>355958.049</v>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n">
+      <c r="A147" s="3" t="n">
         <v>146</v>
       </c>
-      <c r="B147" s="2" t="n">
+      <c r="B147" s="3" t="n">
         <v>1121.004</v>
       </c>
-      <c r="C147" s="2" t="n">
+      <c r="C147" s="3" t="n">
         <v>1120.79</v>
       </c>
-      <c r="D147" s="2" t="n">
+      <c r="D147" s="3" t="n">
         <v>1121</v>
       </c>
-      <c r="E147" s="2" t="n">
+      <c r="E147" s="3" t="n">
         <v>1121.05</v>
       </c>
-      <c r="F147" s="2" t="n">
+      <c r="F147" s="3" t="n">
         <v>1121.17</v>
       </c>
-      <c r="G147" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="H147" s="2" t="n">
+      <c r="G147" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="H147" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I147" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I147" s="2" t="n">
+      <c r="J147" s="3" t="n">
         <v>353776.166</v>
       </c>
-      <c r="J147" s="2" t="n">
+      <c r="K147" s="3" t="n">
         <v>355958.049</v>
       </c>
     </row>
@@ -5196,9 +5646,12 @@
         <v>0</v>
       </c>
       <c r="I148" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" t="n">
         <v>353779.166</v>
       </c>
-      <c r="J148" t="n">
+      <c r="K148" t="n">
         <v>355958.049</v>
       </c>
     </row>
@@ -5228,9 +5681,12 @@
         <v>0</v>
       </c>
       <c r="I149" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" t="n">
         <v>353782.166</v>
       </c>
-      <c r="J149" t="n">
+      <c r="K149" t="n">
         <v>355958.049</v>
       </c>
     </row>
@@ -5260,9 +5716,12 @@
         <v>0</v>
       </c>
       <c r="I150" t="n">
+        <v>0</v>
+      </c>
+      <c r="J150" t="n">
         <v>353785.166</v>
       </c>
-      <c r="J150" t="n">
+      <c r="K150" t="n">
         <v>355958.049</v>
       </c>
     </row>
@@ -5292,9 +5751,12 @@
         <v>0</v>
       </c>
       <c r="I151" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" t="n">
         <v>353788.166</v>
       </c>
-      <c r="J151" t="n">
+      <c r="K151" t="n">
         <v>355958.049</v>
       </c>
     </row>
@@ -5324,9 +5786,12 @@
         <v>0</v>
       </c>
       <c r="I152" t="n">
+        <v>0</v>
+      </c>
+      <c r="J152" t="n">
         <v>353791.166</v>
       </c>
-      <c r="J152" t="n">
+      <c r="K152" t="n">
         <v>355958.049</v>
       </c>
     </row>
@@ -5356,9 +5821,12 @@
         <v>0</v>
       </c>
       <c r="I153" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" t="n">
         <v>353794.166</v>
       </c>
-      <c r="J153" t="n">
+      <c r="K153" t="n">
         <v>355958.049</v>
       </c>
     </row>
@@ -5388,9 +5856,12 @@
         <v>0</v>
       </c>
       <c r="I154" t="n">
+        <v>0</v>
+      </c>
+      <c r="J154" t="n">
         <v>353797.166</v>
       </c>
-      <c r="J154" t="n">
+      <c r="K154" t="n">
         <v>355958.049</v>
       </c>
     </row>
@@ -5420,9 +5891,12 @@
         <v>0</v>
       </c>
       <c r="I155" t="n">
+        <v>0</v>
+      </c>
+      <c r="J155" t="n">
         <v>353740.166</v>
       </c>
-      <c r="J155" t="n">
+      <c r="K155" t="n">
         <v>355955.049</v>
       </c>
     </row>
@@ -5431,16 +5905,16 @@
         <v>155</v>
       </c>
       <c r="B156" s="2" t="n">
-        <v>1113.978</v>
+        <v>1114.409</v>
       </c>
       <c r="C156" s="2" t="n">
         <v>1113.47</v>
       </c>
       <c r="D156" s="2" t="n">
-        <v>1114.73</v>
+        <v>1115.55</v>
       </c>
       <c r="E156" s="2" t="n">
-        <v>1114.64</v>
+        <v>1115.55</v>
       </c>
       <c r="F156" s="2" t="n">
         <v>1113.07</v>
@@ -5452,9 +5926,12 @@
         <v>2</v>
       </c>
       <c r="I156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J156" s="2" t="n">
         <v>353743.166</v>
       </c>
-      <c r="J156" s="2" t="n">
+      <c r="K156" s="2" t="n">
         <v>355955.049</v>
       </c>
     </row>
@@ -5463,19 +5940,19 @@
         <v>156</v>
       </c>
       <c r="B157" s="2" t="n">
-        <v>1114.941</v>
+        <v>1115.55</v>
       </c>
       <c r="C157" s="2" t="n">
-        <v>1114.73</v>
+        <v>1115.55</v>
       </c>
       <c r="D157" s="2" t="n">
-        <v>1115.24</v>
+        <v>1115.55</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>1115.15</v>
+        <v>1115.55</v>
       </c>
       <c r="F157" s="2" t="n">
-        <v>1114.64</v>
+        <v>1115.55</v>
       </c>
       <c r="G157" s="2" t="n">
         <v>9</v>
@@ -5484,9 +5961,12 @@
         <v>4</v>
       </c>
       <c r="I157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J157" s="2" t="n">
         <v>353746.166</v>
       </c>
-      <c r="J157" s="2" t="n">
+      <c r="K157" s="2" t="n">
         <v>355955.049</v>
       </c>
     </row>
@@ -5495,19 +5975,19 @@
         <v>157</v>
       </c>
       <c r="B158" s="2" t="n">
-        <v>1115.448</v>
+        <v>1115.55</v>
       </c>
       <c r="C158" s="2" t="n">
-        <v>1115.24</v>
+        <v>1115.55</v>
       </c>
       <c r="D158" s="2" t="n">
-        <v>1115.75</v>
+        <v>1115.55</v>
       </c>
       <c r="E158" s="2" t="n">
-        <v>1115.66</v>
+        <v>1115.55</v>
       </c>
       <c r="F158" s="2" t="n">
-        <v>1115.15</v>
+        <v>1115.55</v>
       </c>
       <c r="G158" s="2" t="n">
         <v>9</v>
@@ -5516,9 +5996,12 @@
         <v>4</v>
       </c>
       <c r="I158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J158" s="2" t="n">
         <v>353749.166</v>
       </c>
-      <c r="J158" s="2" t="n">
+      <c r="K158" s="2" t="n">
         <v>355955.049</v>
       </c>
     </row>
@@ -5527,19 +6010,19 @@
         <v>158</v>
       </c>
       <c r="B159" s="2" t="n">
-        <v>1115.955</v>
+        <v>1115.55</v>
       </c>
       <c r="C159" s="2" t="n">
-        <v>1115.75</v>
+        <v>1115.55</v>
       </c>
       <c r="D159" s="2" t="n">
-        <v>1116.25</v>
+        <v>1115.55</v>
       </c>
       <c r="E159" s="2" t="n">
-        <v>1116.16</v>
+        <v>1115.55</v>
       </c>
       <c r="F159" s="2" t="n">
-        <v>1115.66</v>
+        <v>1115.55</v>
       </c>
       <c r="G159" s="2" t="n">
         <v>9</v>
@@ -5548,9 +6031,12 @@
         <v>4</v>
       </c>
       <c r="I159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J159" s="2" t="n">
         <v>353752.166</v>
       </c>
-      <c r="J159" s="2" t="n">
+      <c r="K159" s="2" t="n">
         <v>355955.049</v>
       </c>
     </row>
@@ -5559,19 +6045,19 @@
         <v>159</v>
       </c>
       <c r="B160" s="2" t="n">
-        <v>1116.462</v>
+        <v>1115.55</v>
       </c>
       <c r="C160" s="2" t="n">
-        <v>1116.25</v>
+        <v>1115.55</v>
       </c>
       <c r="D160" s="2" t="n">
-        <v>1116.76</v>
+        <v>1115.55</v>
       </c>
       <c r="E160" s="2" t="n">
-        <v>1116.67</v>
+        <v>1115.55</v>
       </c>
       <c r="F160" s="2" t="n">
-        <v>1116.16</v>
+        <v>1115.55</v>
       </c>
       <c r="G160" s="2" t="n">
         <v>9</v>
@@ -5580,9 +6066,12 @@
         <v>4</v>
       </c>
       <c r="I160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" s="2" t="n">
         <v>353755.166</v>
       </c>
-      <c r="J160" s="2" t="n">
+      <c r="K160" s="2" t="n">
         <v>355955.049</v>
       </c>
     </row>
@@ -5591,19 +6080,19 @@
         <v>160</v>
       </c>
       <c r="B161" s="2" t="n">
-        <v>1117.018</v>
+        <v>1115.55</v>
       </c>
       <c r="C161" s="2" t="n">
-        <v>1116.76</v>
+        <v>1115.55</v>
       </c>
       <c r="D161" s="2" t="n">
-        <v>1117.27</v>
+        <v>1115.55</v>
       </c>
       <c r="E161" s="2" t="n">
-        <v>1117.37</v>
+        <v>1115.55</v>
       </c>
       <c r="F161" s="2" t="n">
-        <v>1116.67</v>
+        <v>1115.55</v>
       </c>
       <c r="G161" s="2" t="n">
         <v>9</v>
@@ -5612,9 +6101,12 @@
         <v>4</v>
       </c>
       <c r="I161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J161" s="2" t="n">
         <v>353758.166</v>
       </c>
-      <c r="J161" s="2" t="n">
+      <c r="K161" s="2" t="n">
         <v>355955.049</v>
       </c>
     </row>
@@ -5623,19 +6115,19 @@
         <v>161</v>
       </c>
       <c r="B162" s="2" t="n">
-        <v>1117.57</v>
+        <v>1115.55</v>
       </c>
       <c r="C162" s="2" t="n">
-        <v>1117.27</v>
+        <v>1115.55</v>
       </c>
       <c r="D162" s="2" t="n">
-        <v>1117.77</v>
+        <v>1115.55</v>
       </c>
       <c r="E162" s="2" t="n">
-        <v>1117.87</v>
+        <v>1115.55</v>
       </c>
       <c r="F162" s="2" t="n">
-        <v>1117.37</v>
+        <v>1115.55</v>
       </c>
       <c r="G162" s="2" t="n">
         <v>9</v>
@@ -5644,9 +6136,12 @@
         <v>4</v>
       </c>
       <c r="I162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J162" s="2" t="n">
         <v>353761.166</v>
       </c>
-      <c r="J162" s="2" t="n">
+      <c r="K162" s="2" t="n">
         <v>355955.049</v>
       </c>
     </row>
@@ -5655,19 +6150,19 @@
         <v>162</v>
       </c>
       <c r="B163" s="2" t="n">
-        <v>1118.024</v>
+        <v>1116.211</v>
       </c>
       <c r="C163" s="2" t="n">
-        <v>1117.77</v>
+        <v>1115.55</v>
       </c>
       <c r="D163" s="2" t="n">
         <v>1118.19</v>
       </c>
       <c r="E163" s="2" t="n">
-        <v>1118.26</v>
+        <v>1115.55</v>
       </c>
       <c r="F163" s="2" t="n">
-        <v>1117.87</v>
+        <v>1115.55</v>
       </c>
       <c r="G163" s="2" t="n">
         <v>9</v>
@@ -5676,9 +6171,12 @@
         <v>3</v>
       </c>
       <c r="I163" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J163" s="2" t="n">
         <v>353764.166</v>
       </c>
-      <c r="J163" s="2" t="n">
+      <c r="K163" s="2" t="n">
         <v>355955.049</v>
       </c>
     </row>
@@ -5687,7 +6185,7 @@
         <v>163</v>
       </c>
       <c r="B164" s="2" t="n">
-        <v>1118.808</v>
+        <v>1118.129</v>
       </c>
       <c r="C164" s="2" t="n">
         <v>1118.19</v>
@@ -5699,7 +6197,7 @@
         <v>1119.13</v>
       </c>
       <c r="F164" s="2" t="n">
-        <v>1118.26</v>
+        <v>1115.55</v>
       </c>
       <c r="G164" s="2" t="n">
         <v>9</v>
@@ -5708,9 +6206,12 @@
         <v>1</v>
       </c>
       <c r="I164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J164" s="2" t="n">
         <v>353767.166</v>
       </c>
-      <c r="J164" s="2" t="n">
+      <c r="K164" s="2" t="n">
         <v>355955.049</v>
       </c>
     </row>
@@ -5740,73 +6241,82 @@
         <v>0</v>
       </c>
       <c r="I165" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" t="n">
         <v>353770.166</v>
       </c>
-      <c r="J165" t="n">
+      <c r="K165" t="n">
         <v>355955.049</v>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n">
+      <c r="A166" s="3" t="n">
         <v>165</v>
       </c>
-      <c r="B166" s="2" t="n">
+      <c r="B166" s="3" t="n">
         <v>1121.496</v>
       </c>
-      <c r="C166" s="2" t="n">
+      <c r="C166" s="3" t="n">
         <v>1121.67</v>
       </c>
-      <c r="D166" s="2" t="n">
+      <c r="D166" s="3" t="n">
         <v>1121.17</v>
       </c>
-      <c r="E166" s="2" t="n">
+      <c r="E166" s="3" t="n">
         <v>1121.63</v>
       </c>
-      <c r="F166" s="2" t="n">
+      <c r="F166" s="3" t="n">
         <v>1121.51</v>
       </c>
-      <c r="G166" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="H166" s="2" t="n">
+      <c r="G166" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="H166" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I166" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I166" s="2" t="n">
+      <c r="J166" s="3" t="n">
         <v>353773.166</v>
       </c>
-      <c r="J166" s="2" t="n">
+      <c r="K166" s="3" t="n">
         <v>355955.049</v>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="n">
+      <c r="A167" s="3" t="n">
         <v>166</v>
       </c>
-      <c r="B167" s="2" t="n">
+      <c r="B167" s="3" t="n">
         <v>1121.331</v>
       </c>
-      <c r="C167" s="2" t="n">
+      <c r="C167" s="3" t="n">
         <v>1121.17</v>
       </c>
-      <c r="D167" s="2" t="n">
+      <c r="D167" s="3" t="n">
         <v>1121.05</v>
       </c>
-      <c r="E167" s="2" t="n">
+      <c r="E167" s="3" t="n">
         <v>1121.47</v>
       </c>
-      <c r="F167" s="2" t="n">
+      <c r="F167" s="3" t="n">
         <v>1121.63</v>
       </c>
-      <c r="G167" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="H167" s="2" t="n">
+      <c r="G167" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="H167" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I167" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I167" s="2" t="n">
+      <c r="J167" s="3" t="n">
         <v>353776.166</v>
       </c>
-      <c r="J167" s="2" t="n">
+      <c r="K167" s="3" t="n">
         <v>355955.049</v>
       </c>
     </row>
@@ -5836,9 +6346,12 @@
         <v>0</v>
       </c>
       <c r="I168" t="n">
+        <v>0</v>
+      </c>
+      <c r="J168" t="n">
         <v>353779.166</v>
       </c>
-      <c r="J168" t="n">
+      <c r="K168" t="n">
         <v>355955.049</v>
       </c>
     </row>
@@ -5868,9 +6381,12 @@
         <v>0</v>
       </c>
       <c r="I169" t="n">
+        <v>0</v>
+      </c>
+      <c r="J169" t="n">
         <v>353782.166</v>
       </c>
-      <c r="J169" t="n">
+      <c r="K169" t="n">
         <v>355955.049</v>
       </c>
     </row>
@@ -5900,9 +6416,12 @@
         <v>0</v>
       </c>
       <c r="I170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J170" t="n">
         <v>353785.166</v>
       </c>
-      <c r="J170" t="n">
+      <c r="K170" t="n">
         <v>355955.049</v>
       </c>
     </row>
@@ -5932,9 +6451,12 @@
         <v>0</v>
       </c>
       <c r="I171" t="n">
+        <v>0</v>
+      </c>
+      <c r="J171" t="n">
         <v>353788.166</v>
       </c>
-      <c r="J171" t="n">
+      <c r="K171" t="n">
         <v>355955.049</v>
       </c>
     </row>
@@ -5964,9 +6486,12 @@
         <v>0</v>
       </c>
       <c r="I172" t="n">
+        <v>0</v>
+      </c>
+      <c r="J172" t="n">
         <v>353791.166</v>
       </c>
-      <c r="J172" t="n">
+      <c r="K172" t="n">
         <v>355955.049</v>
       </c>
     </row>
@@ -5996,9 +6521,12 @@
         <v>0</v>
       </c>
       <c r="I173" t="n">
+        <v>0</v>
+      </c>
+      <c r="J173" t="n">
         <v>353794.166</v>
       </c>
-      <c r="J173" t="n">
+      <c r="K173" t="n">
         <v>355955.049</v>
       </c>
     </row>
@@ -6028,9 +6556,12 @@
         <v>0</v>
       </c>
       <c r="I174" t="n">
+        <v>0</v>
+      </c>
+      <c r="J174" t="n">
         <v>353797.166</v>
       </c>
-      <c r="J174" t="n">
+      <c r="K174" t="n">
         <v>355955.049</v>
       </c>
     </row>
@@ -6060,9 +6591,12 @@
         <v>0</v>
       </c>
       <c r="I175" t="n">
+        <v>0</v>
+      </c>
+      <c r="J175" t="n">
         <v>353740.166</v>
       </c>
-      <c r="J175" t="n">
+      <c r="K175" t="n">
         <v>355952.049</v>
       </c>
     </row>
@@ -6071,16 +6605,16 @@
         <v>175</v>
       </c>
       <c r="B176" s="2" t="n">
-        <v>1113.938</v>
+        <v>1114.413</v>
       </c>
       <c r="C176" s="2" t="n">
         <v>1113.07</v>
       </c>
       <c r="D176" s="2" t="n">
-        <v>1114.64</v>
+        <v>1115.55</v>
       </c>
       <c r="E176" s="2" t="n">
-        <v>1114.55</v>
+        <v>1115.55</v>
       </c>
       <c r="F176" s="2" t="n">
         <v>1113.48</v>
@@ -6092,9 +6626,12 @@
         <v>2</v>
       </c>
       <c r="I176" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J176" s="2" t="n">
         <v>353743.166</v>
       </c>
-      <c r="J176" s="2" t="n">
+      <c r="K176" s="2" t="n">
         <v>355952.049</v>
       </c>
     </row>
@@ -6103,19 +6640,19 @@
         <v>176</v>
       </c>
       <c r="B177" s="2" t="n">
-        <v>1114.852</v>
+        <v>1115.55</v>
       </c>
       <c r="C177" s="2" t="n">
-        <v>1114.64</v>
+        <v>1115.55</v>
       </c>
       <c r="D177" s="2" t="n">
-        <v>1115.15</v>
+        <v>1115.55</v>
       </c>
       <c r="E177" s="2" t="n">
-        <v>1115.06</v>
+        <v>1115.55</v>
       </c>
       <c r="F177" s="2" t="n">
-        <v>1114.55</v>
+        <v>1115.55</v>
       </c>
       <c r="G177" s="2" t="n">
         <v>9</v>
@@ -6124,9 +6661,12 @@
         <v>4</v>
       </c>
       <c r="I177" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J177" s="2" t="n">
         <v>353746.166</v>
       </c>
-      <c r="J177" s="2" t="n">
+      <c r="K177" s="2" t="n">
         <v>355952.049</v>
       </c>
     </row>
@@ -6135,19 +6675,19 @@
         <v>177</v>
       </c>
       <c r="B178" s="2" t="n">
-        <v>1115.359</v>
+        <v>1115.55</v>
       </c>
       <c r="C178" s="2" t="n">
-        <v>1115.15</v>
+        <v>1115.55</v>
       </c>
       <c r="D178" s="2" t="n">
-        <v>1115.66</v>
+        <v>1115.55</v>
       </c>
       <c r="E178" s="2" t="n">
-        <v>1115.57</v>
+        <v>1115.55</v>
       </c>
       <c r="F178" s="2" t="n">
-        <v>1115.06</v>
+        <v>1115.55</v>
       </c>
       <c r="G178" s="2" t="n">
         <v>9</v>
@@ -6156,9 +6696,12 @@
         <v>4</v>
       </c>
       <c r="I178" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J178" s="2" t="n">
         <v>353749.166</v>
       </c>
-      <c r="J178" s="2" t="n">
+      <c r="K178" s="2" t="n">
         <v>355952.049</v>
       </c>
     </row>
@@ -6167,19 +6710,19 @@
         <v>178</v>
       </c>
       <c r="B179" s="2" t="n">
-        <v>1115.884</v>
+        <v>1115.55</v>
       </c>
       <c r="C179" s="2" t="n">
-        <v>1115.66</v>
+        <v>1115.55</v>
       </c>
       <c r="D179" s="2" t="n">
-        <v>1116.16</v>
+        <v>1115.55</v>
       </c>
       <c r="E179" s="2" t="n">
-        <v>1116.15</v>
+        <v>1115.55</v>
       </c>
       <c r="F179" s="2" t="n">
-        <v>1115.57</v>
+        <v>1115.55</v>
       </c>
       <c r="G179" s="2" t="n">
         <v>9</v>
@@ -6188,9 +6731,12 @@
         <v>4</v>
       </c>
       <c r="I179" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J179" s="2" t="n">
         <v>353752.166</v>
       </c>
-      <c r="J179" s="2" t="n">
+      <c r="K179" s="2" t="n">
         <v>355952.049</v>
       </c>
     </row>
@@ -6199,19 +6745,19 @@
         <v>179</v>
       </c>
       <c r="B180" s="2" t="n">
-        <v>1116.511</v>
+        <v>1115.55</v>
       </c>
       <c r="C180" s="2" t="n">
-        <v>1116.16</v>
+        <v>1115.55</v>
       </c>
       <c r="D180" s="2" t="n">
-        <v>1116.67</v>
+        <v>1115.55</v>
       </c>
       <c r="E180" s="2" t="n">
-        <v>1117.06</v>
+        <v>1115.55</v>
       </c>
       <c r="F180" s="2" t="n">
-        <v>1116.15</v>
+        <v>1115.55</v>
       </c>
       <c r="G180" s="2" t="n">
         <v>9</v>
@@ -6220,9 +6766,12 @@
         <v>4</v>
       </c>
       <c r="I180" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J180" s="2" t="n">
         <v>353755.166</v>
       </c>
-      <c r="J180" s="2" t="n">
+      <c r="K180" s="2" t="n">
         <v>355952.049</v>
       </c>
     </row>
@@ -6231,19 +6780,19 @@
         <v>180</v>
       </c>
       <c r="B181" s="2" t="n">
-        <v>1117.143</v>
+        <v>1115.55</v>
       </c>
       <c r="C181" s="2" t="n">
-        <v>1116.67</v>
+        <v>1115.55</v>
       </c>
       <c r="D181" s="2" t="n">
-        <v>1117.37</v>
+        <v>1115.55</v>
       </c>
       <c r="E181" s="2" t="n">
-        <v>1117.46</v>
+        <v>1115.55</v>
       </c>
       <c r="F181" s="2" t="n">
-        <v>1117.06</v>
+        <v>1115.55</v>
       </c>
       <c r="G181" s="2" t="n">
         <v>9</v>
@@ -6252,9 +6801,12 @@
         <v>4</v>
       </c>
       <c r="I181" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J181" s="2" t="n">
         <v>353758.166</v>
       </c>
-      <c r="J181" s="2" t="n">
+      <c r="K181" s="2" t="n">
         <v>355952.049</v>
       </c>
     </row>
@@ -6263,19 +6815,19 @@
         <v>181</v>
       </c>
       <c r="B182" s="2" t="n">
-        <v>1117.641</v>
+        <v>1115.55</v>
       </c>
       <c r="C182" s="2" t="n">
-        <v>1117.37</v>
+        <v>1115.55</v>
       </c>
       <c r="D182" s="2" t="n">
-        <v>1117.87</v>
+        <v>1115.55</v>
       </c>
       <c r="E182" s="2" t="n">
-        <v>1117.86</v>
+        <v>1115.55</v>
       </c>
       <c r="F182" s="2" t="n">
-        <v>1117.46</v>
+        <v>1115.55</v>
       </c>
       <c r="G182" s="2" t="n">
         <v>9</v>
@@ -6284,9 +6836,12 @@
         <v>4</v>
       </c>
       <c r="I182" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J182" s="2" t="n">
         <v>353761.166</v>
       </c>
-      <c r="J182" s="2" t="n">
+      <c r="K182" s="2" t="n">
         <v>355952.049</v>
       </c>
     </row>
@@ -6295,19 +6850,19 @@
         <v>182</v>
       </c>
       <c r="B183" s="2" t="n">
-        <v>1118.063</v>
+        <v>1115.55</v>
       </c>
       <c r="C183" s="2" t="n">
-        <v>1117.87</v>
+        <v>1115.55</v>
       </c>
       <c r="D183" s="2" t="n">
-        <v>1118.26</v>
+        <v>1115.55</v>
       </c>
       <c r="E183" s="2" t="n">
-        <v>1118.26</v>
+        <v>1115.55</v>
       </c>
       <c r="F183" s="2" t="n">
-        <v>1117.86</v>
+        <v>1115.55</v>
       </c>
       <c r="G183" s="2" t="n">
         <v>9</v>
@@ -6316,9 +6871,12 @@
         <v>4</v>
       </c>
       <c r="I183" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J183" s="2" t="n">
         <v>353764.166</v>
       </c>
-      <c r="J183" s="2" t="n">
+      <c r="K183" s="2" t="n">
         <v>355952.049</v>
       </c>
     </row>
@@ -6327,10 +6885,10 @@
         <v>183</v>
       </c>
       <c r="B184" s="2" t="n">
-        <v>1118.573</v>
+        <v>1117.217</v>
       </c>
       <c r="C184" s="2" t="n">
-        <v>1118.26</v>
+        <v>1115.55</v>
       </c>
       <c r="D184" s="2" t="n">
         <v>1119.13</v>
@@ -6339,7 +6897,7 @@
         <v>1118.64</v>
       </c>
       <c r="F184" s="2" t="n">
-        <v>1118.26</v>
+        <v>1115.55</v>
       </c>
       <c r="G184" s="2" t="n">
         <v>9</v>
@@ -6348,9 +6906,12 @@
         <v>2</v>
       </c>
       <c r="I184" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J184" s="2" t="n">
         <v>353767.166</v>
       </c>
-      <c r="J184" s="2" t="n">
+      <c r="K184" s="2" t="n">
         <v>355952.049</v>
       </c>
     </row>
@@ -6380,9 +6941,12 @@
         <v>0</v>
       </c>
       <c r="I185" t="n">
+        <v>0</v>
+      </c>
+      <c r="J185" t="n">
         <v>353770.166</v>
       </c>
-      <c r="J185" t="n">
+      <c r="K185" t="n">
         <v>355952.049</v>
       </c>
     </row>
@@ -6412,9 +6976,12 @@
         <v>0</v>
       </c>
       <c r="I186" t="n">
+        <v>0</v>
+      </c>
+      <c r="J186" t="n">
         <v>353773.166</v>
       </c>
-      <c r="J186" t="n">
+      <c r="K186" t="n">
         <v>355952.049</v>
       </c>
     </row>
@@ -6444,9 +7011,12 @@
         <v>0</v>
       </c>
       <c r="I187" t="n">
+        <v>0</v>
+      </c>
+      <c r="J187" t="n">
         <v>353776.166</v>
       </c>
-      <c r="J187" t="n">
+      <c r="K187" t="n">
         <v>355952.049</v>
       </c>
     </row>
@@ -6476,9 +7046,12 @@
         <v>0</v>
       </c>
       <c r="I188" t="n">
+        <v>0</v>
+      </c>
+      <c r="J188" t="n">
         <v>353779.166</v>
       </c>
-      <c r="J188" t="n">
+      <c r="K188" t="n">
         <v>355952.049</v>
       </c>
     </row>
@@ -6508,9 +7081,12 @@
         <v>0</v>
       </c>
       <c r="I189" t="n">
+        <v>0</v>
+      </c>
+      <c r="J189" t="n">
         <v>353782.166</v>
       </c>
-      <c r="J189" t="n">
+      <c r="K189" t="n">
         <v>355952.049</v>
       </c>
     </row>
@@ -6540,9 +7116,12 @@
         <v>0</v>
       </c>
       <c r="I190" t="n">
+        <v>0</v>
+      </c>
+      <c r="J190" t="n">
         <v>353785.166</v>
       </c>
-      <c r="J190" t="n">
+      <c r="K190" t="n">
         <v>355952.049</v>
       </c>
     </row>
@@ -6572,9 +7151,12 @@
         <v>0</v>
       </c>
       <c r="I191" t="n">
+        <v>0</v>
+      </c>
+      <c r="J191" t="n">
         <v>353788.166</v>
       </c>
-      <c r="J191" t="n">
+      <c r="K191" t="n">
         <v>355952.049</v>
       </c>
     </row>
@@ -6604,9 +7186,12 @@
         <v>0</v>
       </c>
       <c r="I192" t="n">
+        <v>0</v>
+      </c>
+      <c r="J192" t="n">
         <v>353791.166</v>
       </c>
-      <c r="J192" t="n">
+      <c r="K192" t="n">
         <v>355952.049</v>
       </c>
     </row>
@@ -6636,9 +7221,12 @@
         <v>0</v>
       </c>
       <c r="I193" t="n">
+        <v>0</v>
+      </c>
+      <c r="J193" t="n">
         <v>353794.166</v>
       </c>
-      <c r="J193" t="n">
+      <c r="K193" t="n">
         <v>355952.049</v>
       </c>
     </row>
@@ -6647,16 +7235,16 @@
         <v>193</v>
       </c>
       <c r="B194" s="2" t="n">
-        <v>1114.101</v>
+        <v>1114.621</v>
       </c>
       <c r="C194" s="2" t="n">
         <v>1113.48</v>
       </c>
       <c r="D194" s="2" t="n">
-        <v>1114.55</v>
+        <v>1115.55</v>
       </c>
       <c r="E194" s="2" t="n">
-        <v>1114.46</v>
+        <v>1115.55</v>
       </c>
       <c r="F194" s="2" t="n">
         <v>1113.9</v>
@@ -6668,9 +7256,12 @@
         <v>2</v>
       </c>
       <c r="I194" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J194" s="2" t="n">
         <v>353743.166</v>
       </c>
-      <c r="J194" s="2" t="n">
+      <c r="K194" s="2" t="n">
         <v>355949.049</v>
       </c>
     </row>
@@ -6679,19 +7270,19 @@
         <v>194</v>
       </c>
       <c r="B195" s="2" t="n">
-        <v>1114.763</v>
+        <v>1115.55</v>
       </c>
       <c r="C195" s="2" t="n">
-        <v>1114.55</v>
+        <v>1115.55</v>
       </c>
       <c r="D195" s="2" t="n">
-        <v>1115.06</v>
+        <v>1115.55</v>
       </c>
       <c r="E195" s="2" t="n">
-        <v>1114.97</v>
+        <v>1115.55</v>
       </c>
       <c r="F195" s="2" t="n">
-        <v>1114.46</v>
+        <v>1115.55</v>
       </c>
       <c r="G195" s="2" t="n">
         <v>9</v>
@@ -6700,9 +7291,12 @@
         <v>4</v>
       </c>
       <c r="I195" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J195" s="2" t="n">
         <v>353746.166</v>
       </c>
-      <c r="J195" s="2" t="n">
+      <c r="K195" s="2" t="n">
         <v>355949.049</v>
       </c>
     </row>
@@ -6711,19 +7305,19 @@
         <v>195</v>
       </c>
       <c r="B196" s="2" t="n">
-        <v>1115.466</v>
+        <v>1115.55</v>
       </c>
       <c r="C196" s="2" t="n">
-        <v>1115.06</v>
+        <v>1115.55</v>
       </c>
       <c r="D196" s="2" t="n">
-        <v>1115.57</v>
+        <v>1115.55</v>
       </c>
       <c r="E196" s="2" t="n">
-        <v>1116.26</v>
+        <v>1115.55</v>
       </c>
       <c r="F196" s="2" t="n">
-        <v>1114.97</v>
+        <v>1115.55</v>
       </c>
       <c r="G196" s="2" t="n">
         <v>9</v>
@@ -6732,9 +7326,12 @@
         <v>4</v>
       </c>
       <c r="I196" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J196" s="2" t="n">
         <v>353749.166</v>
       </c>
-      <c r="J196" s="2" t="n">
+      <c r="K196" s="2" t="n">
         <v>355949.049</v>
       </c>
     </row>
@@ -6743,19 +7340,19 @@
         <v>196</v>
       </c>
       <c r="B197" s="2" t="n">
-        <v>1116.16</v>
+        <v>1115.55</v>
       </c>
       <c r="C197" s="2" t="n">
-        <v>1115.57</v>
+        <v>1115.55</v>
       </c>
       <c r="D197" s="2" t="n">
-        <v>1116.15</v>
+        <v>1115.55</v>
       </c>
       <c r="E197" s="2" t="n">
-        <v>1116.66</v>
+        <v>1115.55</v>
       </c>
       <c r="F197" s="2" t="n">
-        <v>1116.26</v>
+        <v>1115.55</v>
       </c>
       <c r="G197" s="2" t="n">
         <v>9</v>
@@ -6764,9 +7361,12 @@
         <v>4</v>
       </c>
       <c r="I197" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J197" s="2" t="n">
         <v>353752.166</v>
       </c>
-      <c r="J197" s="2" t="n">
+      <c r="K197" s="2" t="n">
         <v>355949.049</v>
       </c>
     </row>
@@ -6775,19 +7375,19 @@
         <v>197</v>
       </c>
       <c r="B198" s="2" t="n">
-        <v>1116.733</v>
+        <v>1115.55</v>
       </c>
       <c r="C198" s="2" t="n">
-        <v>1116.15</v>
+        <v>1115.55</v>
       </c>
       <c r="D198" s="2" t="n">
-        <v>1117.06</v>
+        <v>1115.55</v>
       </c>
       <c r="E198" s="2" t="n">
-        <v>1117.06</v>
+        <v>1115.55</v>
       </c>
       <c r="F198" s="2" t="n">
-        <v>1116.66</v>
+        <v>1115.55</v>
       </c>
       <c r="G198" s="2" t="n">
         <v>9</v>
@@ -6796,9 +7396,12 @@
         <v>4</v>
       </c>
       <c r="I198" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J198" s="2" t="n">
         <v>353755.166</v>
       </c>
-      <c r="J198" s="2" t="n">
+      <c r="K198" s="2" t="n">
         <v>355949.049</v>
       </c>
     </row>
@@ -6807,19 +7410,19 @@
         <v>198</v>
       </c>
       <c r="B199" s="2" t="n">
-        <v>1117.262</v>
+        <v>1115.55</v>
       </c>
       <c r="C199" s="2" t="n">
-        <v>1117.06</v>
+        <v>1115.55</v>
       </c>
       <c r="D199" s="2" t="n">
-        <v>1117.46</v>
+        <v>1115.55</v>
       </c>
       <c r="E199" s="2" t="n">
-        <v>1117.46</v>
+        <v>1115.55</v>
       </c>
       <c r="F199" s="2" t="n">
-        <v>1117.06</v>
+        <v>1115.55</v>
       </c>
       <c r="G199" s="2" t="n">
         <v>9</v>
@@ -6828,9 +7431,12 @@
         <v>4</v>
       </c>
       <c r="I199" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J199" s="2" t="n">
         <v>353758.166</v>
       </c>
-      <c r="J199" s="2" t="n">
+      <c r="K199" s="2" t="n">
         <v>355949.049</v>
       </c>
     </row>
@@ -6839,19 +7445,19 @@
         <v>199</v>
       </c>
       <c r="B200" s="2" t="n">
-        <v>1117.66</v>
+        <v>1115.55</v>
       </c>
       <c r="C200" s="2" t="n">
-        <v>1117.46</v>
+        <v>1115.55</v>
       </c>
       <c r="D200" s="2" t="n">
-        <v>1117.86</v>
+        <v>1115.55</v>
       </c>
       <c r="E200" s="2" t="n">
-        <v>1117.86</v>
+        <v>1115.55</v>
       </c>
       <c r="F200" s="2" t="n">
-        <v>1117.46</v>
+        <v>1115.55</v>
       </c>
       <c r="G200" s="2" t="n">
         <v>9</v>
@@ -6860,9 +7466,12 @@
         <v>4</v>
       </c>
       <c r="I200" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J200" s="2" t="n">
         <v>353761.166</v>
       </c>
-      <c r="J200" s="2" t="n">
+      <c r="K200" s="2" t="n">
         <v>355949.049</v>
       </c>
     </row>
@@ -6871,19 +7480,19 @@
         <v>200</v>
       </c>
       <c r="B201" s="2" t="n">
-        <v>1118.059</v>
+        <v>1115.55</v>
       </c>
       <c r="C201" s="2" t="n">
-        <v>1117.86</v>
+        <v>1115.55</v>
       </c>
       <c r="D201" s="2" t="n">
-        <v>1118.26</v>
+        <v>1115.55</v>
       </c>
       <c r="E201" s="2" t="n">
-        <v>1118.26</v>
+        <v>1115.55</v>
       </c>
       <c r="F201" s="2" t="n">
-        <v>1117.86</v>
+        <v>1115.55</v>
       </c>
       <c r="G201" s="2" t="n">
         <v>9</v>
@@ -6892,9 +7501,12 @@
         <v>4</v>
       </c>
       <c r="I201" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J201" s="2" t="n">
         <v>353764.166</v>
       </c>
-      <c r="J201" s="2" t="n">
+      <c r="K201" s="2" t="n">
         <v>355949.049</v>
       </c>
     </row>
@@ -6903,10 +7515,10 @@
         <v>201</v>
       </c>
       <c r="B202" s="2" t="n">
-        <v>1118.454</v>
+        <v>1117.1</v>
       </c>
       <c r="C202" s="2" t="n">
-        <v>1118.26</v>
+        <v>1115.55</v>
       </c>
       <c r="D202" s="2" t="n">
         <v>1118.64</v>
@@ -6915,7 +7527,7 @@
         <v>1118.66</v>
       </c>
       <c r="F202" s="2" t="n">
-        <v>1118.26</v>
+        <v>1115.55</v>
       </c>
       <c r="G202" s="2" t="n">
         <v>9</v>
@@ -6924,9 +7536,12 @@
         <v>2</v>
       </c>
       <c r="I202" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J202" s="2" t="n">
         <v>353767.166</v>
       </c>
-      <c r="J202" s="2" t="n">
+      <c r="K202" s="2" t="n">
         <v>355949.049</v>
       </c>
     </row>
@@ -6956,9 +7571,12 @@
         <v>0</v>
       </c>
       <c r="I203" t="n">
+        <v>0</v>
+      </c>
+      <c r="J203" t="n">
         <v>353770.166</v>
       </c>
-      <c r="J203" t="n">
+      <c r="K203" t="n">
         <v>355949.049</v>
       </c>
     </row>
@@ -6988,9 +7606,12 @@
         <v>0</v>
       </c>
       <c r="I204" t="n">
+        <v>0</v>
+      </c>
+      <c r="J204" t="n">
         <v>353773.166</v>
       </c>
-      <c r="J204" t="n">
+      <c r="K204" t="n">
         <v>355949.049</v>
       </c>
     </row>
@@ -7020,9 +7641,12 @@
         <v>0</v>
       </c>
       <c r="I205" t="n">
+        <v>0</v>
+      </c>
+      <c r="J205" t="n">
         <v>353776.166</v>
       </c>
-      <c r="J205" t="n">
+      <c r="K205" t="n">
         <v>355949.049</v>
       </c>
     </row>
@@ -7052,9 +7676,12 @@
         <v>0</v>
       </c>
       <c r="I206" t="n">
+        <v>0</v>
+      </c>
+      <c r="J206" t="n">
         <v>353779.166</v>
       </c>
-      <c r="J206" t="n">
+      <c r="K206" t="n">
         <v>355949.049</v>
       </c>
     </row>
@@ -7084,9 +7711,12 @@
         <v>0</v>
       </c>
       <c r="I207" t="n">
+        <v>0</v>
+      </c>
+      <c r="J207" t="n">
         <v>353782.166</v>
       </c>
-      <c r="J207" t="n">
+      <c r="K207" t="n">
         <v>355949.049</v>
       </c>
     </row>
@@ -7116,9 +7746,12 @@
         <v>0</v>
       </c>
       <c r="I208" t="n">
+        <v>0</v>
+      </c>
+      <c r="J208" t="n">
         <v>353785.166</v>
       </c>
-      <c r="J208" t="n">
+      <c r="K208" t="n">
         <v>355949.049</v>
       </c>
     </row>
@@ -7148,9 +7781,12 @@
         <v>0</v>
       </c>
       <c r="I209" t="n">
+        <v>0</v>
+      </c>
+      <c r="J209" t="n">
         <v>353788.166</v>
       </c>
-      <c r="J209" t="n">
+      <c r="K209" t="n">
         <v>355949.049</v>
       </c>
     </row>
@@ -7180,9 +7816,12 @@
         <v>0</v>
       </c>
       <c r="I210" t="n">
+        <v>0</v>
+      </c>
+      <c r="J210" t="n">
         <v>353791.166</v>
       </c>
-      <c r="J210" t="n">
+      <c r="K210" t="n">
         <v>355949.049</v>
       </c>
     </row>
@@ -7212,9 +7851,12 @@
         <v>0</v>
       </c>
       <c r="I211" t="n">
+        <v>0</v>
+      </c>
+      <c r="J211" t="n">
         <v>353794.166</v>
       </c>
-      <c r="J211" t="n">
+      <c r="K211" t="n">
         <v>355949.049</v>
       </c>
     </row>
@@ -7223,13 +7865,13 @@
         <v>211</v>
       </c>
       <c r="B212" s="2" t="n">
-        <v>1114.239</v>
+        <v>1114.51</v>
       </c>
       <c r="C212" s="2" t="n">
         <v>1113.9</v>
       </c>
       <c r="D212" s="2" t="n">
-        <v>1114.46</v>
+        <v>1115.55</v>
       </c>
       <c r="E212" s="2" t="n">
         <v>1114.55</v>
@@ -7244,9 +7886,12 @@
         <v>1</v>
       </c>
       <c r="I212" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J212" s="2" t="n">
         <v>353743.166</v>
       </c>
-      <c r="J212" s="2" t="n">
+      <c r="K212" s="2" t="n">
         <v>355946.049</v>
       </c>
     </row>
@@ -7255,16 +7900,16 @@
         <v>212</v>
       </c>
       <c r="B213" s="2" t="n">
-        <v>1114.968</v>
+        <v>1115.3</v>
       </c>
       <c r="C213" s="2" t="n">
-        <v>1114.46</v>
+        <v>1115.55</v>
       </c>
       <c r="D213" s="2" t="n">
-        <v>1114.97</v>
+        <v>1115.55</v>
       </c>
       <c r="E213" s="2" t="n">
-        <v>1115.89</v>
+        <v>1115.55</v>
       </c>
       <c r="F213" s="2" t="n">
         <v>1114.55</v>
@@ -7276,9 +7921,12 @@
         <v>3</v>
       </c>
       <c r="I213" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J213" s="2" t="n">
         <v>353746.166</v>
       </c>
-      <c r="J213" s="2" t="n">
+      <c r="K213" s="2" t="n">
         <v>355946.049</v>
       </c>
     </row>
@@ -7287,19 +7935,19 @@
         <v>213</v>
       </c>
       <c r="B214" s="2" t="n">
-        <v>1115.86</v>
+        <v>1115.55</v>
       </c>
       <c r="C214" s="2" t="n">
-        <v>1114.97</v>
+        <v>1115.55</v>
       </c>
       <c r="D214" s="2" t="n">
-        <v>1116.26</v>
+        <v>1115.55</v>
       </c>
       <c r="E214" s="2" t="n">
-        <v>1116.32</v>
+        <v>1115.55</v>
       </c>
       <c r="F214" s="2" t="n">
-        <v>1115.89</v>
+        <v>1115.55</v>
       </c>
       <c r="G214" s="2" t="n">
         <v>9</v>
@@ -7308,9 +7956,12 @@
         <v>4</v>
       </c>
       <c r="I214" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J214" s="2" t="n">
         <v>353749.166</v>
       </c>
-      <c r="J214" s="2" t="n">
+      <c r="K214" s="2" t="n">
         <v>355946.049</v>
       </c>
     </row>
@@ -7319,19 +7970,19 @@
         <v>214</v>
       </c>
       <c r="B215" s="2" t="n">
-        <v>1116.5</v>
+        <v>1115.55</v>
       </c>
       <c r="C215" s="2" t="n">
-        <v>1116.26</v>
+        <v>1115.55</v>
       </c>
       <c r="D215" s="2" t="n">
-        <v>1116.66</v>
+        <v>1115.55</v>
       </c>
       <c r="E215" s="2" t="n">
-        <v>1116.76</v>
+        <v>1115.55</v>
       </c>
       <c r="F215" s="2" t="n">
-        <v>1116.32</v>
+        <v>1115.55</v>
       </c>
       <c r="G215" s="2" t="n">
         <v>9</v>
@@ -7340,9 +7991,12 @@
         <v>4</v>
       </c>
       <c r="I215" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J215" s="2" t="n">
         <v>353752.166</v>
       </c>
-      <c r="J215" s="2" t="n">
+      <c r="K215" s="2" t="n">
         <v>355946.049</v>
       </c>
     </row>
@@ -7351,19 +8005,19 @@
         <v>215</v>
       </c>
       <c r="B216" s="2" t="n">
-        <v>1116.917</v>
+        <v>1115.55</v>
       </c>
       <c r="C216" s="2" t="n">
-        <v>1116.66</v>
+        <v>1115.55</v>
       </c>
       <c r="D216" s="2" t="n">
-        <v>1117.06</v>
+        <v>1115.55</v>
       </c>
       <c r="E216" s="2" t="n">
-        <v>1117.19</v>
+        <v>1115.55</v>
       </c>
       <c r="F216" s="2" t="n">
-        <v>1116.76</v>
+        <v>1115.55</v>
       </c>
       <c r="G216" s="2" t="n">
         <v>9</v>
@@ -7372,9 +8026,12 @@
         <v>4</v>
       </c>
       <c r="I216" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J216" s="2" t="n">
         <v>353755.166</v>
       </c>
-      <c r="J216" s="2" t="n">
+      <c r="K216" s="2" t="n">
         <v>355946.049</v>
       </c>
     </row>
@@ -7383,19 +8040,19 @@
         <v>216</v>
       </c>
       <c r="B217" s="2" t="n">
-        <v>1117.334</v>
+        <v>1115.55</v>
       </c>
       <c r="C217" s="2" t="n">
-        <v>1117.06</v>
+        <v>1115.55</v>
       </c>
       <c r="D217" s="2" t="n">
-        <v>1117.46</v>
+        <v>1115.55</v>
       </c>
       <c r="E217" s="2" t="n">
-        <v>1117.63</v>
+        <v>1115.55</v>
       </c>
       <c r="F217" s="2" t="n">
-        <v>1117.19</v>
+        <v>1115.55</v>
       </c>
       <c r="G217" s="2" t="n">
         <v>9</v>
@@ -7404,9 +8061,12 @@
         <v>4</v>
       </c>
       <c r="I217" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J217" s="2" t="n">
         <v>353758.166</v>
       </c>
-      <c r="J217" s="2" t="n">
+      <c r="K217" s="2" t="n">
         <v>355946.049</v>
       </c>
     </row>
@@ -7415,19 +8075,19 @@
         <v>217</v>
       </c>
       <c r="B218" s="2" t="n">
-        <v>1117.751</v>
+        <v>1115.55</v>
       </c>
       <c r="C218" s="2" t="n">
-        <v>1117.46</v>
+        <v>1115.55</v>
       </c>
       <c r="D218" s="2" t="n">
-        <v>1117.86</v>
+        <v>1115.55</v>
       </c>
       <c r="E218" s="2" t="n">
-        <v>1118.06</v>
+        <v>1115.55</v>
       </c>
       <c r="F218" s="2" t="n">
-        <v>1117.63</v>
+        <v>1115.55</v>
       </c>
       <c r="G218" s="2" t="n">
         <v>9</v>
@@ -7436,9 +8096,12 @@
         <v>4</v>
       </c>
       <c r="I218" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J218" s="2" t="n">
         <v>353761.166</v>
       </c>
-      <c r="J218" s="2" t="n">
+      <c r="K218" s="2" t="n">
         <v>355946.049</v>
       </c>
     </row>
@@ -7447,19 +8110,19 @@
         <v>218</v>
       </c>
       <c r="B219" s="2" t="n">
-        <v>1118.168</v>
+        <v>1115.55</v>
       </c>
       <c r="C219" s="2" t="n">
-        <v>1117.86</v>
+        <v>1115.55</v>
       </c>
       <c r="D219" s="2" t="n">
-        <v>1118.26</v>
+        <v>1115.55</v>
       </c>
       <c r="E219" s="2" t="n">
-        <v>1118.5</v>
+        <v>1115.55</v>
       </c>
       <c r="F219" s="2" t="n">
-        <v>1118.06</v>
+        <v>1115.55</v>
       </c>
       <c r="G219" s="2" t="n">
         <v>9</v>
@@ -7468,9 +8131,12 @@
         <v>4</v>
       </c>
       <c r="I219" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J219" s="2" t="n">
         <v>353764.166</v>
       </c>
-      <c r="J219" s="2" t="n">
+      <c r="K219" s="2" t="n">
         <v>355946.049</v>
       </c>
     </row>
@@ -7479,10 +8145,10 @@
         <v>219</v>
       </c>
       <c r="B220" s="2" t="n">
-        <v>1118.585</v>
+        <v>1117.171</v>
       </c>
       <c r="C220" s="2" t="n">
-        <v>1118.26</v>
+        <v>1115.55</v>
       </c>
       <c r="D220" s="2" t="n">
         <v>1118.66</v>
@@ -7491,7 +8157,7 @@
         <v>1118.93</v>
       </c>
       <c r="F220" s="2" t="n">
-        <v>1118.5</v>
+        <v>1115.55</v>
       </c>
       <c r="G220" s="2" t="n">
         <v>9</v>
@@ -7500,9 +8166,12 @@
         <v>2</v>
       </c>
       <c r="I220" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J220" s="2" t="n">
         <v>353767.166</v>
       </c>
-      <c r="J220" s="2" t="n">
+      <c r="K220" s="2" t="n">
         <v>355946.049</v>
       </c>
     </row>
@@ -7532,9 +8201,12 @@
         <v>0</v>
       </c>
       <c r="I221" t="n">
+        <v>0</v>
+      </c>
+      <c r="J221" t="n">
         <v>353770.166</v>
       </c>
-      <c r="J221" t="n">
+      <c r="K221" t="n">
         <v>355946.049</v>
       </c>
     </row>
@@ -7564,9 +8236,12 @@
         <v>0</v>
       </c>
       <c r="I222" t="n">
+        <v>0</v>
+      </c>
+      <c r="J222" t="n">
         <v>353773.166</v>
       </c>
-      <c r="J222" t="n">
+      <c r="K222" t="n">
         <v>355946.049</v>
       </c>
     </row>
@@ -7596,9 +8271,12 @@
         <v>0</v>
       </c>
       <c r="I223" t="n">
+        <v>0</v>
+      </c>
+      <c r="J223" t="n">
         <v>353776.166</v>
       </c>
-      <c r="J223" t="n">
+      <c r="K223" t="n">
         <v>355946.049</v>
       </c>
     </row>
@@ -7628,9 +8306,12 @@
         <v>0</v>
       </c>
       <c r="I224" t="n">
+        <v>0</v>
+      </c>
+      <c r="J224" t="n">
         <v>353779.166</v>
       </c>
-      <c r="J224" t="n">
+      <c r="K224" t="n">
         <v>355946.049</v>
       </c>
     </row>
@@ -7660,9 +8341,12 @@
         <v>0</v>
       </c>
       <c r="I225" t="n">
+        <v>0</v>
+      </c>
+      <c r="J225" t="n">
         <v>353782.166</v>
       </c>
-      <c r="J225" t="n">
+      <c r="K225" t="n">
         <v>355946.049</v>
       </c>
     </row>
@@ -7692,9 +8376,12 @@
         <v>0</v>
       </c>
       <c r="I226" t="n">
+        <v>0</v>
+      </c>
+      <c r="J226" t="n">
         <v>353785.166</v>
       </c>
-      <c r="J226" t="n">
+      <c r="K226" t="n">
         <v>355946.049</v>
       </c>
     </row>
@@ -7724,9 +8411,12 @@
         <v>0</v>
       </c>
       <c r="I227" t="n">
+        <v>0</v>
+      </c>
+      <c r="J227" t="n">
         <v>353788.166</v>
       </c>
-      <c r="J227" t="n">
+      <c r="K227" t="n">
         <v>355946.049</v>
       </c>
     </row>
@@ -7756,9 +8446,12 @@
         <v>0</v>
       </c>
       <c r="I228" t="n">
+        <v>0</v>
+      </c>
+      <c r="J228" t="n">
         <v>353791.166</v>
       </c>
-      <c r="J228" t="n">
+      <c r="K228" t="n">
         <v>355946.049</v>
       </c>
     </row>
@@ -7788,9 +8481,12 @@
         <v>0</v>
       </c>
       <c r="I229" t="n">
+        <v>0</v>
+      </c>
+      <c r="J229" t="n">
         <v>353794.166</v>
       </c>
-      <c r="J229" t="n">
+      <c r="K229" t="n">
         <v>355946.049</v>
       </c>
     </row>
@@ -7820,9 +8516,12 @@
         <v>0</v>
       </c>
       <c r="I230" t="n">
+        <v>0</v>
+      </c>
+      <c r="J230" t="n">
         <v>353743.166</v>
       </c>
-      <c r="J230" t="n">
+      <c r="K230" t="n">
         <v>355943.049</v>
       </c>
     </row>
@@ -7831,16 +8530,16 @@
         <v>230</v>
       </c>
       <c r="B231" s="2" t="n">
-        <v>1115.041</v>
+        <v>1114.973</v>
       </c>
       <c r="C231" s="2" t="n">
         <v>1114.55</v>
       </c>
       <c r="D231" s="2" t="n">
-        <v>1115.89</v>
+        <v>1115.55</v>
       </c>
       <c r="E231" s="2" t="n">
-        <v>1115.48</v>
+        <v>1115.55</v>
       </c>
       <c r="F231" s="2" t="n">
         <v>1114.24</v>
@@ -7852,9 +8551,12 @@
         <v>2</v>
       </c>
       <c r="I231" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J231" s="2" t="n">
         <v>353746.166</v>
       </c>
-      <c r="J231" s="2" t="n">
+      <c r="K231" s="2" t="n">
         <v>355943.049</v>
       </c>
     </row>
@@ -7863,19 +8565,19 @@
         <v>231</v>
       </c>
       <c r="B232" s="2" t="n">
-        <v>1116.201</v>
+        <v>1115.55</v>
       </c>
       <c r="C232" s="2" t="n">
-        <v>1115.89</v>
+        <v>1115.55</v>
       </c>
       <c r="D232" s="2" t="n">
-        <v>1116.32</v>
+        <v>1115.55</v>
       </c>
       <c r="E232" s="2" t="n">
-        <v>1117.11</v>
+        <v>1115.55</v>
       </c>
       <c r="F232" s="2" t="n">
-        <v>1115.48</v>
+        <v>1115.55</v>
       </c>
       <c r="G232" s="2" t="n">
         <v>9</v>
@@ -7884,9 +8586,12 @@
         <v>4</v>
       </c>
       <c r="I232" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J232" s="2" t="n">
         <v>353749.166</v>
       </c>
-      <c r="J232" s="2" t="n">
+      <c r="K232" s="2" t="n">
         <v>355943.049</v>
       </c>
     </row>
@@ -7895,19 +8600,19 @@
         <v>232</v>
       </c>
       <c r="B233" s="2" t="n">
-        <v>1117.233</v>
+        <v>1115.55</v>
       </c>
       <c r="C233" s="2" t="n">
-        <v>1116.32</v>
+        <v>1115.55</v>
       </c>
       <c r="D233" s="2" t="n">
-        <v>1116.76</v>
+        <v>1115.55</v>
       </c>
       <c r="E233" s="2" t="n">
-        <v>1118.74</v>
+        <v>1115.55</v>
       </c>
       <c r="F233" s="2" t="n">
-        <v>1117.11</v>
+        <v>1115.55</v>
       </c>
       <c r="G233" s="2" t="n">
         <v>9</v>
@@ -7916,9 +8621,12 @@
         <v>4</v>
       </c>
       <c r="I233" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J233" s="2" t="n">
         <v>353752.166</v>
       </c>
-      <c r="J233" s="2" t="n">
+      <c r="K233" s="2" t="n">
         <v>355943.049</v>
       </c>
     </row>
@@ -7927,19 +8635,19 @@
         <v>233</v>
       </c>
       <c r="B234" s="2" t="n">
-        <v>1118.265</v>
+        <v>1115.55</v>
       </c>
       <c r="C234" s="2" t="n">
-        <v>1116.76</v>
+        <v>1115.55</v>
       </c>
       <c r="D234" s="2" t="n">
-        <v>1117.19</v>
+        <v>1115.55</v>
       </c>
       <c r="E234" s="2" t="n">
-        <v>1120.37</v>
+        <v>1115.55</v>
       </c>
       <c r="F234" s="2" t="n">
-        <v>1118.74</v>
+        <v>1115.55</v>
       </c>
       <c r="G234" s="2" t="n">
         <v>9</v>
@@ -7948,9 +8656,12 @@
         <v>4</v>
       </c>
       <c r="I234" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J234" s="2" t="n">
         <v>353755.166</v>
       </c>
-      <c r="J234" s="2" t="n">
+      <c r="K234" s="2" t="n">
         <v>355943.049</v>
       </c>
     </row>
@@ -7959,19 +8670,19 @@
         <v>234</v>
       </c>
       <c r="B235" s="2" t="n">
-        <v>1119.297</v>
+        <v>1115.55</v>
       </c>
       <c r="C235" s="2" t="n">
-        <v>1117.19</v>
+        <v>1115.55</v>
       </c>
       <c r="D235" s="2" t="n">
-        <v>1117.63</v>
+        <v>1115.55</v>
       </c>
       <c r="E235" s="2" t="n">
-        <v>1122</v>
+        <v>1115.55</v>
       </c>
       <c r="F235" s="2" t="n">
-        <v>1120.37</v>
+        <v>1115.55</v>
       </c>
       <c r="G235" s="2" t="n">
         <v>9</v>
@@ -7980,9 +8691,12 @@
         <v>4</v>
       </c>
       <c r="I235" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J235" s="2" t="n">
         <v>353758.166</v>
       </c>
-      <c r="J235" s="2" t="n">
+      <c r="K235" s="2" t="n">
         <v>355943.049</v>
       </c>
     </row>
@@ -7991,19 +8705,19 @@
         <v>235</v>
       </c>
       <c r="B236" s="2" t="n">
-        <v>1120.329</v>
+        <v>1115.55</v>
       </c>
       <c r="C236" s="2" t="n">
-        <v>1117.63</v>
+        <v>1115.55</v>
       </c>
       <c r="D236" s="2" t="n">
-        <v>1118.06</v>
+        <v>1115.55</v>
       </c>
       <c r="E236" s="2" t="n">
-        <v>1123.63</v>
+        <v>1115.55</v>
       </c>
       <c r="F236" s="2" t="n">
-        <v>1122</v>
+        <v>1115.55</v>
       </c>
       <c r="G236" s="2" t="n">
         <v>9</v>
@@ -8012,9 +8726,12 @@
         <v>4</v>
       </c>
       <c r="I236" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J236" s="2" t="n">
         <v>353761.166</v>
       </c>
-      <c r="J236" s="2" t="n">
+      <c r="K236" s="2" t="n">
         <v>355943.049</v>
       </c>
     </row>
@@ -8023,19 +8740,19 @@
         <v>236</v>
       </c>
       <c r="B237" s="2" t="n">
-        <v>1121.361</v>
+        <v>1115.55</v>
       </c>
       <c r="C237" s="2" t="n">
-        <v>1118.06</v>
+        <v>1115.55</v>
       </c>
       <c r="D237" s="2" t="n">
-        <v>1118.5</v>
+        <v>1115.55</v>
       </c>
       <c r="E237" s="2" t="n">
-        <v>1125.26</v>
+        <v>1115.55</v>
       </c>
       <c r="F237" s="2" t="n">
-        <v>1123.63</v>
+        <v>1115.55</v>
       </c>
       <c r="G237" s="2" t="n">
         <v>9</v>
@@ -8044,9 +8761,12 @@
         <v>4</v>
       </c>
       <c r="I237" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J237" s="2" t="n">
         <v>353764.166</v>
       </c>
-      <c r="J237" s="2" t="n">
+      <c r="K237" s="2" t="n">
         <v>355943.049</v>
       </c>
     </row>
@@ -8055,10 +8775,10 @@
         <v>237</v>
       </c>
       <c r="B238" s="2" t="n">
-        <v>1122.393</v>
+        <v>1119.23</v>
       </c>
       <c r="C238" s="2" t="n">
-        <v>1118.5</v>
+        <v>1115.55</v>
       </c>
       <c r="D238" s="2" t="n">
         <v>1118.93</v>
@@ -8067,7 +8787,7 @@
         <v>1126.89</v>
       </c>
       <c r="F238" s="2" t="n">
-        <v>1125.26</v>
+        <v>1115.55</v>
       </c>
       <c r="G238" s="2" t="n">
         <v>9</v>
@@ -8076,9 +8796,12 @@
         <v>2</v>
       </c>
       <c r="I238" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J238" s="2" t="n">
         <v>353767.166</v>
       </c>
-      <c r="J238" s="2" t="n">
+      <c r="K238" s="2" t="n">
         <v>355943.049</v>
       </c>
     </row>
@@ -8108,9 +8831,12 @@
         <v>0</v>
       </c>
       <c r="I239" t="n">
+        <v>0</v>
+      </c>
+      <c r="J239" t="n">
         <v>353770.166</v>
       </c>
-      <c r="J239" t="n">
+      <c r="K239" t="n">
         <v>355943.049</v>
       </c>
     </row>
@@ -8140,9 +8866,12 @@
         <v>0</v>
       </c>
       <c r="I240" t="n">
+        <v>0</v>
+      </c>
+      <c r="J240" t="n">
         <v>353773.166</v>
       </c>
-      <c r="J240" t="n">
+      <c r="K240" t="n">
         <v>355943.049</v>
       </c>
     </row>
@@ -8172,9 +8901,12 @@
         <v>0</v>
       </c>
       <c r="I241" t="n">
+        <v>0</v>
+      </c>
+      <c r="J241" t="n">
         <v>353776.166</v>
       </c>
-      <c r="J241" t="n">
+      <c r="K241" t="n">
         <v>355943.049</v>
       </c>
     </row>
@@ -8204,9 +8936,12 @@
         <v>0</v>
       </c>
       <c r="I242" t="n">
+        <v>0</v>
+      </c>
+      <c r="J242" t="n">
         <v>353779.166</v>
       </c>
-      <c r="J242" t="n">
+      <c r="K242" t="n">
         <v>355943.049</v>
       </c>
     </row>
@@ -8236,9 +8971,12 @@
         <v>0</v>
       </c>
       <c r="I243" t="n">
+        <v>0</v>
+      </c>
+      <c r="J243" t="n">
         <v>353782.166</v>
       </c>
-      <c r="J243" t="n">
+      <c r="K243" t="n">
         <v>355943.049</v>
       </c>
     </row>
@@ -8268,9 +9006,12 @@
         <v>0</v>
       </c>
       <c r="I244" t="n">
+        <v>0</v>
+      </c>
+      <c r="J244" t="n">
         <v>353785.166</v>
       </c>
-      <c r="J244" t="n">
+      <c r="K244" t="n">
         <v>355943.049</v>
       </c>
     </row>
@@ -8300,9 +9041,12 @@
         <v>0</v>
       </c>
       <c r="I245" t="n">
+        <v>0</v>
+      </c>
+      <c r="J245" t="n">
         <v>353788.166</v>
       </c>
-      <c r="J245" t="n">
+      <c r="K245" t="n">
         <v>355943.049</v>
       </c>
     </row>
@@ -8332,9 +9076,12 @@
         <v>0</v>
       </c>
       <c r="I246" t="n">
+        <v>0</v>
+      </c>
+      <c r="J246" t="n">
         <v>353791.166</v>
       </c>
-      <c r="J246" t="n">
+      <c r="K246" t="n">
         <v>355943.049</v>
       </c>
     </row>
@@ -8364,9 +9111,12 @@
         <v>0</v>
       </c>
       <c r="I247" t="n">
+        <v>0</v>
+      </c>
+      <c r="J247" t="n">
         <v>353794.166</v>
       </c>
-      <c r="J247" t="n">
+      <c r="K247" t="n">
         <v>355943.049</v>
       </c>
     </row>
@@ -8396,9 +9146,12 @@
         <v>0</v>
       </c>
       <c r="I248" t="n">
+        <v>0</v>
+      </c>
+      <c r="J248" t="n">
         <v>353743.166</v>
       </c>
-      <c r="J248" t="n">
+      <c r="K248" t="n">
         <v>355940.049</v>
       </c>
     </row>
@@ -8407,16 +9160,16 @@
         <v>248</v>
       </c>
       <c r="B249" s="2" t="n">
-        <v>1115.674</v>
+        <v>1114.995</v>
       </c>
       <c r="C249" s="2" t="n">
         <v>1114.24</v>
       </c>
       <c r="D249" s="2" t="n">
-        <v>1115.48</v>
+        <v>1115.55</v>
       </c>
       <c r="E249" s="2" t="n">
-        <v>1118.33</v>
+        <v>1115.55</v>
       </c>
       <c r="F249" s="2" t="n">
         <v>1114.64</v>
@@ -8428,9 +9181,12 @@
         <v>2</v>
       </c>
       <c r="I249" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J249" s="2" t="n">
         <v>353746.166</v>
       </c>
-      <c r="J249" s="2" t="n">
+      <c r="K249" s="2" t="n">
         <v>355940.049</v>
       </c>
     </row>
@@ -8439,19 +9195,19 @@
         <v>249</v>
       </c>
       <c r="B250" s="2" t="n">
-        <v>1117.721</v>
+        <v>1115.55</v>
       </c>
       <c r="C250" s="2" t="n">
-        <v>1115.48</v>
+        <v>1115.55</v>
       </c>
       <c r="D250" s="2" t="n">
-        <v>1117.11</v>
+        <v>1115.55</v>
       </c>
       <c r="E250" s="2" t="n">
-        <v>1119.96</v>
+        <v>1115.55</v>
       </c>
       <c r="F250" s="2" t="n">
-        <v>1118.33</v>
+        <v>1115.55</v>
       </c>
       <c r="G250" s="2" t="n">
         <v>9</v>
@@ -8460,9 +9216,12 @@
         <v>4</v>
       </c>
       <c r="I250" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J250" s="2" t="n">
         <v>353749.166</v>
       </c>
-      <c r="J250" s="2" t="n">
+      <c r="K250" s="2" t="n">
         <v>355940.049</v>
       </c>
     </row>
@@ -8471,19 +9230,19 @@
         <v>250</v>
       </c>
       <c r="B251" s="2" t="n">
-        <v>1119.35</v>
+        <v>1115.55</v>
       </c>
       <c r="C251" s="2" t="n">
-        <v>1117.11</v>
+        <v>1115.55</v>
       </c>
       <c r="D251" s="2" t="n">
-        <v>1118.74</v>
+        <v>1115.55</v>
       </c>
       <c r="E251" s="2" t="n">
-        <v>1121.59</v>
+        <v>1115.55</v>
       </c>
       <c r="F251" s="2" t="n">
-        <v>1119.96</v>
+        <v>1115.55</v>
       </c>
       <c r="G251" s="2" t="n">
         <v>9</v>
@@ -8492,9 +9251,12 @@
         <v>4</v>
       </c>
       <c r="I251" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J251" s="2" t="n">
         <v>353752.166</v>
       </c>
-      <c r="J251" s="2" t="n">
+      <c r="K251" s="2" t="n">
         <v>355940.049</v>
       </c>
     </row>
@@ -8503,19 +9265,19 @@
         <v>251</v>
       </c>
       <c r="B252" s="2" t="n">
-        <v>1120.979</v>
+        <v>1115.55</v>
       </c>
       <c r="C252" s="2" t="n">
-        <v>1118.74</v>
+        <v>1115.55</v>
       </c>
       <c r="D252" s="2" t="n">
-        <v>1120.37</v>
+        <v>1115.55</v>
       </c>
       <c r="E252" s="2" t="n">
-        <v>1123.22</v>
+        <v>1115.55</v>
       </c>
       <c r="F252" s="2" t="n">
-        <v>1121.59</v>
+        <v>1115.55</v>
       </c>
       <c r="G252" s="2" t="n">
         <v>9</v>
@@ -8524,9 +9286,12 @@
         <v>4</v>
       </c>
       <c r="I252" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J252" s="2" t="n">
         <v>353755.166</v>
       </c>
-      <c r="J252" s="2" t="n">
+      <c r="K252" s="2" t="n">
         <v>355940.049</v>
       </c>
     </row>
@@ -8535,19 +9300,19 @@
         <v>252</v>
       </c>
       <c r="B253" s="2" t="n">
-        <v>1122.387</v>
+        <v>1115.55</v>
       </c>
       <c r="C253" s="2" t="n">
-        <v>1120.37</v>
+        <v>1115.55</v>
       </c>
       <c r="D253" s="2" t="n">
-        <v>1122</v>
+        <v>1115.55</v>
       </c>
       <c r="E253" s="2" t="n">
-        <v>1123.96</v>
+        <v>1115.55</v>
       </c>
       <c r="F253" s="2" t="n">
-        <v>1123.22</v>
+        <v>1115.55</v>
       </c>
       <c r="G253" s="2" t="n">
         <v>9</v>
@@ -8556,9 +9321,12 @@
         <v>4</v>
       </c>
       <c r="I253" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J253" s="2" t="n">
         <v>353758.166</v>
       </c>
-      <c r="J253" s="2" t="n">
+      <c r="K253" s="2" t="n">
         <v>355940.049</v>
       </c>
     </row>
@@ -8567,19 +9335,19 @@
         <v>253</v>
       </c>
       <c r="B254" s="2" t="n">
-        <v>1123.35</v>
+        <v>1115.55</v>
       </c>
       <c r="C254" s="2" t="n">
-        <v>1122</v>
+        <v>1115.55</v>
       </c>
       <c r="D254" s="2" t="n">
-        <v>1123.63</v>
+        <v>1115.55</v>
       </c>
       <c r="E254" s="2" t="n">
-        <v>1123.81</v>
+        <v>1115.55</v>
       </c>
       <c r="F254" s="2" t="n">
-        <v>1123.96</v>
+        <v>1115.55</v>
       </c>
       <c r="G254" s="2" t="n">
         <v>9</v>
@@ -8588,9 +9356,12 @@
         <v>4</v>
       </c>
       <c r="I254" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J254" s="2" t="n">
         <v>353761.166</v>
       </c>
-      <c r="J254" s="2" t="n">
+      <c r="K254" s="2" t="n">
         <v>355940.049</v>
       </c>
     </row>
@@ -8599,19 +9370,19 @@
         <v>254</v>
       </c>
       <c r="B255" s="2" t="n">
-        <v>1124.092</v>
+        <v>1115.55</v>
       </c>
       <c r="C255" s="2" t="n">
-        <v>1123.63</v>
+        <v>1115.55</v>
       </c>
       <c r="D255" s="2" t="n">
-        <v>1125.26</v>
+        <v>1115.55</v>
       </c>
       <c r="E255" s="2" t="n">
-        <v>1123.67</v>
+        <v>1115.55</v>
       </c>
       <c r="F255" s="2" t="n">
-        <v>1123.81</v>
+        <v>1115.55</v>
       </c>
       <c r="G255" s="2" t="n">
         <v>9</v>
@@ -8620,9 +9391,12 @@
         <v>4</v>
       </c>
       <c r="I255" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J255" s="2" t="n">
         <v>353764.166</v>
       </c>
-      <c r="J255" s="2" t="n">
+      <c r="K255" s="2" t="n">
         <v>355940.049</v>
       </c>
     </row>
@@ -8631,19 +9405,19 @@
         <v>255</v>
       </c>
       <c r="B256" s="2" t="n">
-        <v>1124.833</v>
+        <v>1118.385</v>
       </c>
       <c r="C256" s="2" t="n">
-        <v>1125.26</v>
+        <v>1115.55</v>
       </c>
       <c r="D256" s="2" t="n">
         <v>1126.89</v>
       </c>
       <c r="E256" s="2" t="n">
-        <v>1123.52</v>
+        <v>1115.55</v>
       </c>
       <c r="F256" s="2" t="n">
-        <v>1123.67</v>
+        <v>1115.55</v>
       </c>
       <c r="G256" s="2" t="n">
         <v>9</v>
@@ -8652,9 +9426,12 @@
         <v>3</v>
       </c>
       <c r="I256" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J256" s="2" t="n">
         <v>353767.166</v>
       </c>
-      <c r="J256" s="2" t="n">
+      <c r="K256" s="2" t="n">
         <v>355940.049</v>
       </c>
     </row>
@@ -8663,7 +9440,7 @@
         <v>256</v>
       </c>
       <c r="B257" s="2" t="n">
-        <v>1124.25</v>
+        <v>1122.257</v>
       </c>
       <c r="C257" s="2" t="n">
         <v>1126.89</v>
@@ -8675,7 +9452,7 @@
         <v>1122.28</v>
       </c>
       <c r="F257" s="2" t="n">
-        <v>1123.52</v>
+        <v>1115.55</v>
       </c>
       <c r="G257" s="2" t="n">
         <v>9</v>
@@ -8684,9 +9461,12 @@
         <v>1</v>
       </c>
       <c r="I257" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J257" s="2" t="n">
         <v>353770.166</v>
       </c>
-      <c r="J257" s="2" t="n">
+      <c r="K257" s="2" t="n">
         <v>355940.049</v>
       </c>
     </row>
@@ -8716,9 +9496,12 @@
         <v>0</v>
       </c>
       <c r="I258" t="n">
+        <v>0</v>
+      </c>
+      <c r="J258" t="n">
         <v>353773.166</v>
       </c>
-      <c r="J258" t="n">
+      <c r="K258" t="n">
         <v>355940.049</v>
       </c>
     </row>
@@ -8748,9 +9531,12 @@
         <v>0</v>
       </c>
       <c r="I259" t="n">
+        <v>0</v>
+      </c>
+      <c r="J259" t="n">
         <v>353776.166</v>
       </c>
-      <c r="J259" t="n">
+      <c r="K259" t="n">
         <v>355940.049</v>
       </c>
     </row>
@@ -8780,9 +9566,12 @@
         <v>0</v>
       </c>
       <c r="I260" t="n">
+        <v>0</v>
+      </c>
+      <c r="J260" t="n">
         <v>353779.166</v>
       </c>
-      <c r="J260" t="n">
+      <c r="K260" t="n">
         <v>355940.049</v>
       </c>
     </row>
@@ -8812,9 +9601,12 @@
         <v>0</v>
       </c>
       <c r="I261" t="n">
+        <v>0</v>
+      </c>
+      <c r="J261" t="n">
         <v>353782.166</v>
       </c>
-      <c r="J261" t="n">
+      <c r="K261" t="n">
         <v>355940.049</v>
       </c>
     </row>
@@ -8844,9 +9636,12 @@
         <v>0</v>
       </c>
       <c r="I262" t="n">
+        <v>0</v>
+      </c>
+      <c r="J262" t="n">
         <v>353785.166</v>
       </c>
-      <c r="J262" t="n">
+      <c r="K262" t="n">
         <v>355940.049</v>
       </c>
     </row>
@@ -8876,9 +9671,12 @@
         <v>0</v>
       </c>
       <c r="I263" t="n">
+        <v>0</v>
+      </c>
+      <c r="J263" t="n">
         <v>353788.166</v>
       </c>
-      <c r="J263" t="n">
+      <c r="K263" t="n">
         <v>355940.049</v>
       </c>
     </row>
@@ -8908,9 +9706,12 @@
         <v>0</v>
       </c>
       <c r="I264" t="n">
+        <v>0</v>
+      </c>
+      <c r="J264" t="n">
         <v>353791.166</v>
       </c>
-      <c r="J264" t="n">
+      <c r="K264" t="n">
         <v>355940.049</v>
       </c>
     </row>
@@ -8940,9 +9741,12 @@
         <v>0</v>
       </c>
       <c r="I265" t="n">
+        <v>0</v>
+      </c>
+      <c r="J265" t="n">
         <v>353794.166</v>
       </c>
-      <c r="J265" t="n">
+      <c r="K265" t="n">
         <v>355940.049</v>
       </c>
     </row>
@@ -8951,13 +9755,13 @@
         <v>265</v>
       </c>
       <c r="B266" s="2" t="n">
-        <v>1117.294</v>
+        <v>1116.599</v>
       </c>
       <c r="C266" s="2" t="n">
         <v>1114.64</v>
       </c>
       <c r="D266" s="2" t="n">
-        <v>1118.33</v>
+        <v>1115.55</v>
       </c>
       <c r="E266" s="2" t="n">
         <v>1121.17</v>
@@ -8972,9 +9776,12 @@
         <v>1</v>
       </c>
       <c r="I266" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J266" s="2" t="n">
         <v>353746.166</v>
       </c>
-      <c r="J266" s="2" t="n">
+      <c r="K266" s="2" t="n">
         <v>355937.049</v>
       </c>
     </row>
@@ -8983,16 +9790,16 @@
         <v>266</v>
       </c>
       <c r="B267" s="2" t="n">
-        <v>1120.122</v>
+        <v>1116.956</v>
       </c>
       <c r="C267" s="2" t="n">
-        <v>1118.33</v>
+        <v>1115.55</v>
       </c>
       <c r="D267" s="2" t="n">
-        <v>1119.96</v>
+        <v>1115.55</v>
       </c>
       <c r="E267" s="2" t="n">
-        <v>1121.03</v>
+        <v>1115.55</v>
       </c>
       <c r="F267" s="2" t="n">
         <v>1121.17</v>
@@ -9004,9 +9811,12 @@
         <v>3</v>
       </c>
       <c r="I267" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J267" s="2" t="n">
         <v>353749.166</v>
       </c>
-      <c r="J267" s="2" t="n">
+      <c r="K267" s="2" t="n">
         <v>355937.049</v>
       </c>
     </row>
@@ -9015,19 +9825,19 @@
         <v>267</v>
       </c>
       <c r="B268" s="2" t="n">
-        <v>1120.863</v>
+        <v>1115.55</v>
       </c>
       <c r="C268" s="2" t="n">
-        <v>1119.96</v>
+        <v>1115.55</v>
       </c>
       <c r="D268" s="2" t="n">
-        <v>1121.59</v>
+        <v>1115.55</v>
       </c>
       <c r="E268" s="2" t="n">
-        <v>1120.88</v>
+        <v>1115.55</v>
       </c>
       <c r="F268" s="2" t="n">
-        <v>1121.03</v>
+        <v>1115.55</v>
       </c>
       <c r="G268" s="2" t="n">
         <v>9</v>
@@ -9036,9 +9846,12 @@
         <v>4</v>
       </c>
       <c r="I268" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J268" s="2" t="n">
         <v>353752.166</v>
       </c>
-      <c r="J268" s="2" t="n">
+      <c r="K268" s="2" t="n">
         <v>355937.049</v>
       </c>
     </row>
@@ -9047,19 +9860,19 @@
         <v>268</v>
       </c>
       <c r="B269" s="2" t="n">
-        <v>1121.605</v>
+        <v>1115.55</v>
       </c>
       <c r="C269" s="2" t="n">
-        <v>1121.59</v>
+        <v>1115.55</v>
       </c>
       <c r="D269" s="2" t="n">
-        <v>1123.22</v>
+        <v>1115.55</v>
       </c>
       <c r="E269" s="2" t="n">
-        <v>1120.74</v>
+        <v>1115.55</v>
       </c>
       <c r="F269" s="2" t="n">
-        <v>1120.88</v>
+        <v>1115.55</v>
       </c>
       <c r="G269" s="2" t="n">
         <v>9</v>
@@ -9068,9 +9881,12 @@
         <v>4</v>
       </c>
       <c r="I269" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J269" s="2" t="n">
         <v>353755.166</v>
       </c>
-      <c r="J269" s="2" t="n">
+      <c r="K269" s="2" t="n">
         <v>355937.049</v>
       </c>
     </row>
@@ -9079,19 +9895,19 @@
         <v>269</v>
       </c>
       <c r="B270" s="2" t="n">
-        <v>1122.125</v>
+        <v>1115.55</v>
       </c>
       <c r="C270" s="2" t="n">
-        <v>1123.22</v>
+        <v>1115.55</v>
       </c>
       <c r="D270" s="2" t="n">
-        <v>1123.96</v>
+        <v>1115.55</v>
       </c>
       <c r="E270" s="2" t="n">
-        <v>1120.59</v>
+        <v>1115.55</v>
       </c>
       <c r="F270" s="2" t="n">
-        <v>1120.74</v>
+        <v>1115.55</v>
       </c>
       <c r="G270" s="2" t="n">
         <v>9</v>
@@ -9100,9 +9916,12 @@
         <v>4</v>
       </c>
       <c r="I270" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J270" s="2" t="n">
         <v>353758.166</v>
       </c>
-      <c r="J270" s="2" t="n">
+      <c r="K270" s="2" t="n">
         <v>355937.049</v>
       </c>
     </row>
@@ -9111,19 +9930,19 @@
         <v>270</v>
       </c>
       <c r="B271" s="2" t="n">
-        <v>1122.201</v>
+        <v>1115.55</v>
       </c>
       <c r="C271" s="2" t="n">
-        <v>1123.96</v>
+        <v>1115.55</v>
       </c>
       <c r="D271" s="2" t="n">
-        <v>1123.81</v>
+        <v>1115.55</v>
       </c>
       <c r="E271" s="2" t="n">
-        <v>1120.44</v>
+        <v>1115.55</v>
       </c>
       <c r="F271" s="2" t="n">
-        <v>1120.59</v>
+        <v>1115.55</v>
       </c>
       <c r="G271" s="2" t="n">
         <v>9</v>
@@ -9132,9 +9951,12 @@
         <v>4</v>
       </c>
       <c r="I271" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J271" s="2" t="n">
         <v>353761.166</v>
       </c>
-      <c r="J271" s="2" t="n">
+      <c r="K271" s="2" t="n">
         <v>355937.049</v>
       </c>
     </row>
@@ -9143,19 +9965,19 @@
         <v>271</v>
       </c>
       <c r="B272" s="2" t="n">
-        <v>1122.055</v>
+        <v>1115.55</v>
       </c>
       <c r="C272" s="2" t="n">
-        <v>1123.81</v>
+        <v>1115.55</v>
       </c>
       <c r="D272" s="2" t="n">
-        <v>1123.67</v>
+        <v>1115.55</v>
       </c>
       <c r="E272" s="2" t="n">
-        <v>1120.3</v>
+        <v>1115.55</v>
       </c>
       <c r="F272" s="2" t="n">
-        <v>1120.44</v>
+        <v>1115.55</v>
       </c>
       <c r="G272" s="2" t="n">
         <v>9</v>
@@ -9164,9 +9986,12 @@
         <v>4</v>
       </c>
       <c r="I272" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J272" s="2" t="n">
         <v>353764.166</v>
       </c>
-      <c r="J272" s="2" t="n">
+      <c r="K272" s="2" t="n">
         <v>355937.049</v>
       </c>
     </row>
@@ -9175,19 +10000,19 @@
         <v>272</v>
       </c>
       <c r="B273" s="2" t="n">
-        <v>1121.909</v>
+        <v>1115.55</v>
       </c>
       <c r="C273" s="2" t="n">
-        <v>1123.67</v>
+        <v>1115.55</v>
       </c>
       <c r="D273" s="2" t="n">
-        <v>1123.52</v>
+        <v>1115.55</v>
       </c>
       <c r="E273" s="2" t="n">
-        <v>1120.15</v>
+        <v>1115.55</v>
       </c>
       <c r="F273" s="2" t="n">
-        <v>1120.3</v>
+        <v>1115.55</v>
       </c>
       <c r="G273" s="2" t="n">
         <v>9</v>
@@ -9196,9 +10021,12 @@
         <v>4</v>
       </c>
       <c r="I273" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J273" s="2" t="n">
         <v>353767.166</v>
       </c>
-      <c r="J273" s="2" t="n">
+      <c r="K273" s="2" t="n">
         <v>355937.049</v>
       </c>
     </row>
@@ -9207,10 +10035,10 @@
         <v>273</v>
       </c>
       <c r="B274" s="2" t="n">
-        <v>1121.359</v>
+        <v>1118.216</v>
       </c>
       <c r="C274" s="2" t="n">
-        <v>1123.52</v>
+        <v>1115.55</v>
       </c>
       <c r="D274" s="2" t="n">
         <v>1122.28</v>
@@ -9219,7 +10047,7 @@
         <v>1119.49</v>
       </c>
       <c r="F274" s="2" t="n">
-        <v>1120.15</v>
+        <v>1115.55</v>
       </c>
       <c r="G274" s="2" t="n">
         <v>9</v>
@@ -9228,9 +10056,12 @@
         <v>2</v>
       </c>
       <c r="I274" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J274" s="2" t="n">
         <v>353770.166</v>
       </c>
-      <c r="J274" s="2" t="n">
+      <c r="K274" s="2" t="n">
         <v>355937.049</v>
       </c>
     </row>
@@ -9260,9 +10091,12 @@
         <v>0</v>
       </c>
       <c r="I275" t="n">
+        <v>0</v>
+      </c>
+      <c r="J275" t="n">
         <v>353773.166</v>
       </c>
-      <c r="J275" t="n">
+      <c r="K275" t="n">
         <v>355937.049</v>
       </c>
     </row>
@@ -9292,9 +10126,12 @@
         <v>0</v>
       </c>
       <c r="I276" t="n">
+        <v>0</v>
+      </c>
+      <c r="J276" t="n">
         <v>353776.166</v>
       </c>
-      <c r="J276" t="n">
+      <c r="K276" t="n">
         <v>355937.049</v>
       </c>
     </row>
@@ -9324,9 +10161,12 @@
         <v>0</v>
       </c>
       <c r="I277" t="n">
+        <v>0</v>
+      </c>
+      <c r="J277" t="n">
         <v>353779.166</v>
       </c>
-      <c r="J277" t="n">
+      <c r="K277" t="n">
         <v>355937.049</v>
       </c>
     </row>
@@ -9356,9 +10196,12 @@
         <v>0</v>
       </c>
       <c r="I278" t="n">
+        <v>0</v>
+      </c>
+      <c r="J278" t="n">
         <v>353782.166</v>
       </c>
-      <c r="J278" t="n">
+      <c r="K278" t="n">
         <v>355937.049</v>
       </c>
     </row>
@@ -9388,9 +10231,12 @@
         <v>0</v>
       </c>
       <c r="I279" t="n">
+        <v>0</v>
+      </c>
+      <c r="J279" t="n">
         <v>353785.166</v>
       </c>
-      <c r="J279" t="n">
+      <c r="K279" t="n">
         <v>355937.049</v>
       </c>
     </row>
@@ -9420,9 +10266,12 @@
         <v>0</v>
       </c>
       <c r="I280" t="n">
+        <v>0</v>
+      </c>
+      <c r="J280" t="n">
         <v>353788.166</v>
       </c>
-      <c r="J280" t="n">
+      <c r="K280" t="n">
         <v>355937.049</v>
       </c>
     </row>
@@ -9452,9 +10301,12 @@
         <v>0</v>
       </c>
       <c r="I281" t="n">
+        <v>0</v>
+      </c>
+      <c r="J281" t="n">
         <v>353791.166</v>
       </c>
-      <c r="J281" t="n">
+      <c r="K281" t="n">
         <v>355937.049</v>
       </c>
     </row>
@@ -9484,9 +10336,12 @@
         <v>0</v>
       </c>
       <c r="I282" t="n">
+        <v>0</v>
+      </c>
+      <c r="J282" t="n">
         <v>353794.166</v>
       </c>
-      <c r="J282" t="n">
+      <c r="K282" t="n">
         <v>355937.049</v>
       </c>
     </row>
@@ -9516,9 +10371,12 @@
         <v>0</v>
       </c>
       <c r="I283" t="n">
+        <v>0</v>
+      </c>
+      <c r="J283" t="n">
         <v>353746.166</v>
       </c>
-      <c r="J283" t="n">
+      <c r="K283" t="n">
         <v>355934.049</v>
       </c>
     </row>
@@ -9527,16 +10385,16 @@
         <v>283</v>
       </c>
       <c r="B284" s="2" t="n">
-        <v>1120.676</v>
+        <v>1118.164</v>
       </c>
       <c r="C284" s="2" t="n">
         <v>1121.17</v>
       </c>
       <c r="D284" s="2" t="n">
-        <v>1121.03</v>
+        <v>1115.55</v>
       </c>
       <c r="E284" s="2" t="n">
-        <v>1120.12</v>
+        <v>1115.55</v>
       </c>
       <c r="F284" s="2" t="n">
         <v>1120.38</v>
@@ -9548,9 +10406,12 @@
         <v>2</v>
       </c>
       <c r="I284" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J284" s="2" t="n">
         <v>353749.166</v>
       </c>
-      <c r="J284" s="2" t="n">
+      <c r="K284" s="2" t="n">
         <v>355934.049</v>
       </c>
     </row>
@@ -9559,19 +10420,19 @@
         <v>284</v>
       </c>
       <c r="B285" s="2" t="n">
-        <v>1120.472</v>
+        <v>1115.55</v>
       </c>
       <c r="C285" s="2" t="n">
-        <v>1121.03</v>
+        <v>1115.55</v>
       </c>
       <c r="D285" s="2" t="n">
-        <v>1120.88</v>
+        <v>1115.55</v>
       </c>
       <c r="E285" s="2" t="n">
-        <v>1119.86</v>
+        <v>1115.55</v>
       </c>
       <c r="F285" s="2" t="n">
-        <v>1120.12</v>
+        <v>1115.55</v>
       </c>
       <c r="G285" s="2" t="n">
         <v>9</v>
@@ -9580,9 +10441,12 @@
         <v>4</v>
       </c>
       <c r="I285" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J285" s="2" t="n">
         <v>353752.166</v>
       </c>
-      <c r="J285" s="2" t="n">
+      <c r="K285" s="2" t="n">
         <v>355934.049</v>
       </c>
     </row>
@@ -9591,19 +10455,19 @@
         <v>285</v>
       </c>
       <c r="B286" s="2" t="n">
-        <v>1120.268</v>
+        <v>1115.55</v>
       </c>
       <c r="C286" s="2" t="n">
-        <v>1120.88</v>
+        <v>1115.55</v>
       </c>
       <c r="D286" s="2" t="n">
-        <v>1120.74</v>
+        <v>1115.55</v>
       </c>
       <c r="E286" s="2" t="n">
-        <v>1119.6</v>
+        <v>1115.55</v>
       </c>
       <c r="F286" s="2" t="n">
-        <v>1119.86</v>
+        <v>1115.55</v>
       </c>
       <c r="G286" s="2" t="n">
         <v>9</v>
@@ -9612,9 +10476,12 @@
         <v>4</v>
       </c>
       <c r="I286" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J286" s="2" t="n">
         <v>353755.166</v>
       </c>
-      <c r="J286" s="2" t="n">
+      <c r="K286" s="2" t="n">
         <v>355934.049</v>
       </c>
     </row>
@@ -9623,19 +10490,19 @@
         <v>286</v>
       </c>
       <c r="B287" s="2" t="n">
-        <v>1120.064</v>
+        <v>1115.55</v>
       </c>
       <c r="C287" s="2" t="n">
-        <v>1120.74</v>
+        <v>1115.55</v>
       </c>
       <c r="D287" s="2" t="n">
-        <v>1120.59</v>
+        <v>1115.55</v>
       </c>
       <c r="E287" s="2" t="n">
-        <v>1119.34</v>
+        <v>1115.55</v>
       </c>
       <c r="F287" s="2" t="n">
-        <v>1119.6</v>
+        <v>1115.55</v>
       </c>
       <c r="G287" s="2" t="n">
         <v>9</v>
@@ -9644,9 +10511,12 @@
         <v>4</v>
       </c>
       <c r="I287" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J287" s="2" t="n">
         <v>353758.166</v>
       </c>
-      <c r="J287" s="2" t="n">
+      <c r="K287" s="2" t="n">
         <v>355934.049</v>
       </c>
     </row>
@@ -9655,19 +10525,19 @@
         <v>287</v>
       </c>
       <c r="B288" s="2" t="n">
-        <v>1119.86</v>
+        <v>1115.55</v>
       </c>
       <c r="C288" s="2" t="n">
-        <v>1120.59</v>
+        <v>1115.55</v>
       </c>
       <c r="D288" s="2" t="n">
-        <v>1120.44</v>
+        <v>1115.55</v>
       </c>
       <c r="E288" s="2" t="n">
-        <v>1119.07</v>
+        <v>1115.55</v>
       </c>
       <c r="F288" s="2" t="n">
-        <v>1119.34</v>
+        <v>1115.55</v>
       </c>
       <c r="G288" s="2" t="n">
         <v>9</v>
@@ -9676,9 +10546,12 @@
         <v>4</v>
       </c>
       <c r="I288" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J288" s="2" t="n">
         <v>353761.166</v>
       </c>
-      <c r="J288" s="2" t="n">
+      <c r="K288" s="2" t="n">
         <v>355934.049</v>
       </c>
     </row>
@@ -9687,19 +10560,19 @@
         <v>288</v>
       </c>
       <c r="B289" s="2" t="n">
-        <v>1119.656</v>
+        <v>1115.55</v>
       </c>
       <c r="C289" s="2" t="n">
-        <v>1120.44</v>
+        <v>1115.55</v>
       </c>
       <c r="D289" s="2" t="n">
-        <v>1120.3</v>
+        <v>1115.55</v>
       </c>
       <c r="E289" s="2" t="n">
-        <v>1118.81</v>
+        <v>1115.55</v>
       </c>
       <c r="F289" s="2" t="n">
-        <v>1119.07</v>
+        <v>1115.55</v>
       </c>
       <c r="G289" s="2" t="n">
         <v>9</v>
@@ -9708,9 +10581,12 @@
         <v>4</v>
       </c>
       <c r="I289" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J289" s="2" t="n">
         <v>353764.166</v>
       </c>
-      <c r="J289" s="2" t="n">
+      <c r="K289" s="2" t="n">
         <v>355934.049</v>
       </c>
     </row>
@@ -9719,19 +10595,19 @@
         <v>289</v>
       </c>
       <c r="B290" s="2" t="n">
-        <v>1119.453</v>
+        <v>1115.55</v>
       </c>
       <c r="C290" s="2" t="n">
-        <v>1120.3</v>
+        <v>1115.55</v>
       </c>
       <c r="D290" s="2" t="n">
-        <v>1120.15</v>
+        <v>1115.55</v>
       </c>
       <c r="E290" s="2" t="n">
-        <v>1118.55</v>
+        <v>1115.55</v>
       </c>
       <c r="F290" s="2" t="n">
-        <v>1118.81</v>
+        <v>1115.55</v>
       </c>
       <c r="G290" s="2" t="n">
         <v>9</v>
@@ -9740,9 +10616,12 @@
         <v>4</v>
       </c>
       <c r="I290" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J290" s="2" t="n">
         <v>353767.166</v>
       </c>
-      <c r="J290" s="2" t="n">
+      <c r="K290" s="2" t="n">
         <v>355934.049</v>
       </c>
     </row>
@@ -9751,10 +10630,10 @@
         <v>290</v>
       </c>
       <c r="B291" s="2" t="n">
-        <v>1119.4</v>
+        <v>1117.5</v>
       </c>
       <c r="C291" s="2" t="n">
-        <v>1120.15</v>
+        <v>1115.55</v>
       </c>
       <c r="D291" s="2" t="n">
         <v>1119.49</v>
@@ -9763,7 +10642,7 @@
         <v>1119.41</v>
       </c>
       <c r="F291" s="2" t="n">
-        <v>1118.55</v>
+        <v>1115.55</v>
       </c>
       <c r="G291" s="2" t="n">
         <v>9</v>
@@ -9772,9 +10651,12 @@
         <v>2</v>
       </c>
       <c r="I291" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J291" s="2" t="n">
         <v>353770.166</v>
       </c>
-      <c r="J291" s="2" t="n">
+      <c r="K291" s="2" t="n">
         <v>355934.049</v>
       </c>
     </row>
@@ -9804,9 +10686,12 @@
         <v>0</v>
       </c>
       <c r="I292" t="n">
+        <v>0</v>
+      </c>
+      <c r="J292" t="n">
         <v>353773.166</v>
       </c>
-      <c r="J292" t="n">
+      <c r="K292" t="n">
         <v>355934.049</v>
       </c>
     </row>
@@ -9836,9 +10721,12 @@
         <v>0</v>
       </c>
       <c r="I293" t="n">
+        <v>0</v>
+      </c>
+      <c r="J293" t="n">
         <v>353776.166</v>
       </c>
-      <c r="J293" t="n">
+      <c r="K293" t="n">
         <v>355934.049</v>
       </c>
     </row>
@@ -9868,9 +10756,12 @@
         <v>0</v>
       </c>
       <c r="I294" t="n">
+        <v>0</v>
+      </c>
+      <c r="J294" t="n">
         <v>353779.166</v>
       </c>
-      <c r="J294" t="n">
+      <c r="K294" t="n">
         <v>355934.049</v>
       </c>
     </row>
@@ -9900,9 +10791,12 @@
         <v>0</v>
       </c>
       <c r="I295" t="n">
+        <v>0</v>
+      </c>
+      <c r="J295" t="n">
         <v>353782.166</v>
       </c>
-      <c r="J295" t="n">
+      <c r="K295" t="n">
         <v>355934.049</v>
       </c>
     </row>
@@ -9932,9 +10826,12 @@
         <v>0</v>
       </c>
       <c r="I296" t="n">
+        <v>0</v>
+      </c>
+      <c r="J296" t="n">
         <v>353785.166</v>
       </c>
-      <c r="J296" t="n">
+      <c r="K296" t="n">
         <v>355934.049</v>
       </c>
     </row>
@@ -9964,9 +10861,12 @@
         <v>0</v>
       </c>
       <c r="I297" t="n">
+        <v>0</v>
+      </c>
+      <c r="J297" t="n">
         <v>353788.166</v>
       </c>
-      <c r="J297" t="n">
+      <c r="K297" t="n">
         <v>355934.049</v>
       </c>
     </row>
@@ -9996,9 +10896,12 @@
         <v>0</v>
       </c>
       <c r="I298" t="n">
+        <v>0</v>
+      </c>
+      <c r="J298" t="n">
         <v>353791.166</v>
       </c>
-      <c r="J298" t="n">
+      <c r="K298" t="n">
         <v>355934.049</v>
       </c>
     </row>
@@ -10028,9 +10931,12 @@
         <v>0</v>
       </c>
       <c r="I299" t="n">
+        <v>0</v>
+      </c>
+      <c r="J299" t="n">
         <v>353746.166</v>
       </c>
-      <c r="J299" t="n">
+      <c r="K299" t="n">
         <v>355931.049</v>
       </c>
     </row>
@@ -10039,16 +10945,16 @@
         <v>299</v>
       </c>
       <c r="B300" s="2" t="n">
-        <v>1119.716</v>
+        <v>1117.66</v>
       </c>
       <c r="C300" s="2" t="n">
         <v>1120.38</v>
       </c>
       <c r="D300" s="2" t="n">
-        <v>1120.12</v>
+        <v>1115.55</v>
       </c>
       <c r="E300" s="2" t="n">
-        <v>1119.2</v>
+        <v>1115.55</v>
       </c>
       <c r="F300" s="2" t="n">
         <v>1119.16</v>
@@ -10060,9 +10966,12 @@
         <v>2</v>
       </c>
       <c r="I300" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J300" s="2" t="n">
         <v>353749.166</v>
       </c>
-      <c r="J300" s="2" t="n">
+      <c r="K300" s="2" t="n">
         <v>355931.049</v>
       </c>
     </row>
@@ -10071,19 +10980,19 @@
         <v>300</v>
       </c>
       <c r="B301" s="2" t="n">
-        <v>1119.542</v>
+        <v>1115.55</v>
       </c>
       <c r="C301" s="2" t="n">
-        <v>1120.12</v>
+        <v>1115.55</v>
       </c>
       <c r="D301" s="2" t="n">
-        <v>1119.86</v>
+        <v>1115.55</v>
       </c>
       <c r="E301" s="2" t="n">
-        <v>1118.99</v>
+        <v>1115.55</v>
       </c>
       <c r="F301" s="2" t="n">
-        <v>1119.2</v>
+        <v>1115.55</v>
       </c>
       <c r="G301" s="2" t="n">
         <v>9</v>
@@ -10092,9 +11001,12 @@
         <v>4</v>
       </c>
       <c r="I301" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J301" s="2" t="n">
         <v>353752.166</v>
       </c>
-      <c r="J301" s="2" t="n">
+      <c r="K301" s="2" t="n">
         <v>355931.049</v>
       </c>
     </row>
@@ -10103,19 +11015,19 @@
         <v>301</v>
       </c>
       <c r="B302" s="2" t="n">
-        <v>1119.293</v>
+        <v>1115.55</v>
       </c>
       <c r="C302" s="2" t="n">
-        <v>1119.86</v>
+        <v>1115.55</v>
       </c>
       <c r="D302" s="2" t="n">
-        <v>1119.6</v>
+        <v>1115.55</v>
       </c>
       <c r="E302" s="2" t="n">
-        <v>1118.73</v>
+        <v>1115.55</v>
       </c>
       <c r="F302" s="2" t="n">
-        <v>1118.99</v>
+        <v>1115.55</v>
       </c>
       <c r="G302" s="2" t="n">
         <v>9</v>
@@ -10124,9 +11036,12 @@
         <v>4</v>
       </c>
       <c r="I302" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J302" s="2" t="n">
         <v>353755.166</v>
       </c>
-      <c r="J302" s="2" t="n">
+      <c r="K302" s="2" t="n">
         <v>355931.049</v>
       </c>
     </row>
@@ -10135,19 +11050,19 @@
         <v>302</v>
       </c>
       <c r="B303" s="2" t="n">
-        <v>1119.032</v>
+        <v>1115.55</v>
       </c>
       <c r="C303" s="2" t="n">
-        <v>1119.6</v>
+        <v>1115.55</v>
       </c>
       <c r="D303" s="2" t="n">
-        <v>1119.34</v>
+        <v>1115.55</v>
       </c>
       <c r="E303" s="2" t="n">
-        <v>1118.47</v>
+        <v>1115.55</v>
       </c>
       <c r="F303" s="2" t="n">
-        <v>1118.73</v>
+        <v>1115.55</v>
       </c>
       <c r="G303" s="2" t="n">
         <v>9</v>
@@ -10156,9 +11071,12 @@
         <v>4</v>
       </c>
       <c r="I303" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J303" s="2" t="n">
         <v>353758.166</v>
       </c>
-      <c r="J303" s="2" t="n">
+      <c r="K303" s="2" t="n">
         <v>355931.049</v>
       </c>
     </row>
@@ -10167,19 +11085,19 @@
         <v>303</v>
       </c>
       <c r="B304" s="2" t="n">
-        <v>1118.771</v>
+        <v>1115.55</v>
       </c>
       <c r="C304" s="2" t="n">
-        <v>1119.34</v>
+        <v>1115.55</v>
       </c>
       <c r="D304" s="2" t="n">
-        <v>1119.07</v>
+        <v>1115.55</v>
       </c>
       <c r="E304" s="2" t="n">
-        <v>1118.21</v>
+        <v>1115.55</v>
       </c>
       <c r="F304" s="2" t="n">
-        <v>1118.47</v>
+        <v>1115.55</v>
       </c>
       <c r="G304" s="2" t="n">
         <v>9</v>
@@ -10188,9 +11106,12 @@
         <v>4</v>
       </c>
       <c r="I304" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J304" s="2" t="n">
         <v>353761.166</v>
       </c>
-      <c r="J304" s="2" t="n">
+      <c r="K304" s="2" t="n">
         <v>355931.049</v>
       </c>
     </row>
@@ -10199,19 +11120,19 @@
         <v>304</v>
       </c>
       <c r="B305" s="2" t="n">
-        <v>1118.509</v>
+        <v>1115.55</v>
       </c>
       <c r="C305" s="2" t="n">
-        <v>1119.07</v>
+        <v>1115.55</v>
       </c>
       <c r="D305" s="2" t="n">
-        <v>1118.81</v>
+        <v>1115.55</v>
       </c>
       <c r="E305" s="2" t="n">
-        <v>1117.94</v>
+        <v>1115.55</v>
       </c>
       <c r="F305" s="2" t="n">
-        <v>1118.21</v>
+        <v>1115.55</v>
       </c>
       <c r="G305" s="2" t="n">
         <v>9</v>
@@ -10220,9 +11141,12 @@
         <v>4</v>
       </c>
       <c r="I305" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J305" s="2" t="n">
         <v>353764.166</v>
       </c>
-      <c r="J305" s="2" t="n">
+      <c r="K305" s="2" t="n">
         <v>355931.049</v>
       </c>
     </row>
@@ -10231,19 +11155,19 @@
         <v>305</v>
       </c>
       <c r="B306" s="2" t="n">
-        <v>1118.293</v>
+        <v>1115.55</v>
       </c>
       <c r="C306" s="2" t="n">
-        <v>1118.81</v>
+        <v>1115.55</v>
       </c>
       <c r="D306" s="2" t="n">
-        <v>1118.55</v>
+        <v>1115.55</v>
       </c>
       <c r="E306" s="2" t="n">
-        <v>1117.87</v>
+        <v>1115.55</v>
       </c>
       <c r="F306" s="2" t="n">
-        <v>1117.94</v>
+        <v>1115.55</v>
       </c>
       <c r="G306" s="2" t="n">
         <v>9</v>
@@ -10252,9 +11176,12 @@
         <v>4</v>
       </c>
       <c r="I306" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J306" s="2" t="n">
         <v>353767.166</v>
       </c>
-      <c r="J306" s="2" t="n">
+      <c r="K306" s="2" t="n">
         <v>355931.049</v>
       </c>
     </row>
@@ -10263,10 +11190,10 @@
         <v>306</v>
       </c>
       <c r="B307" s="2" t="n">
-        <v>1118.728</v>
+        <v>1117.399</v>
       </c>
       <c r="C307" s="2" t="n">
-        <v>1118.55</v>
+        <v>1115.55</v>
       </c>
       <c r="D307" s="2" t="n">
         <v>1119.41</v>
@@ -10275,7 +11202,7 @@
         <v>1119.09</v>
       </c>
       <c r="F307" s="2" t="n">
-        <v>1117.87</v>
+        <v>1115.55</v>
       </c>
       <c r="G307" s="2" t="n">
         <v>9</v>
@@ -10284,9 +11211,12 @@
         <v>2</v>
       </c>
       <c r="I307" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J307" s="2" t="n">
         <v>353770.166</v>
       </c>
-      <c r="J307" s="2" t="n">
+      <c r="K307" s="2" t="n">
         <v>355931.049</v>
       </c>
     </row>
@@ -10316,9 +11246,12 @@
         <v>0</v>
       </c>
       <c r="I308" t="n">
+        <v>0</v>
+      </c>
+      <c r="J308" t="n">
         <v>353773.166</v>
       </c>
-      <c r="J308" t="n">
+      <c r="K308" t="n">
         <v>355931.049</v>
       </c>
     </row>
@@ -10348,9 +11281,12 @@
         <v>0</v>
       </c>
       <c r="I309" t="n">
+        <v>0</v>
+      </c>
+      <c r="J309" t="n">
         <v>353776.166</v>
       </c>
-      <c r="J309" t="n">
+      <c r="K309" t="n">
         <v>355931.049</v>
       </c>
     </row>
@@ -10380,9 +11316,12 @@
         <v>0</v>
       </c>
       <c r="I310" t="n">
+        <v>0</v>
+      </c>
+      <c r="J310" t="n">
         <v>353779.166</v>
       </c>
-      <c r="J310" t="n">
+      <c r="K310" t="n">
         <v>355931.049</v>
       </c>
     </row>
@@ -10412,9 +11351,12 @@
         <v>0</v>
       </c>
       <c r="I311" t="n">
+        <v>0</v>
+      </c>
+      <c r="J311" t="n">
         <v>353782.166</v>
       </c>
-      <c r="J311" t="n">
+      <c r="K311" t="n">
         <v>355931.049</v>
       </c>
     </row>
@@ -10444,9 +11386,12 @@
         <v>0</v>
       </c>
       <c r="I312" t="n">
+        <v>0</v>
+      </c>
+      <c r="J312" t="n">
         <v>353785.166</v>
       </c>
-      <c r="J312" t="n">
+      <c r="K312" t="n">
         <v>355931.049</v>
       </c>
     </row>
@@ -10476,9 +11421,12 @@
         <v>0</v>
       </c>
       <c r="I313" t="n">
+        <v>0</v>
+      </c>
+      <c r="J313" t="n">
         <v>353788.166</v>
       </c>
-      <c r="J313" t="n">
+      <c r="K313" t="n">
         <v>355931.049</v>
       </c>
     </row>
@@ -10508,9 +11456,12 @@
         <v>0</v>
       </c>
       <c r="I314" t="n">
+        <v>0</v>
+      </c>
+      <c r="J314" t="n">
         <v>353791.166</v>
       </c>
-      <c r="J314" t="n">
+      <c r="K314" t="n">
         <v>355931.049</v>
       </c>
     </row>
@@ -10540,9 +11491,12 @@
         <v>0</v>
       </c>
       <c r="I315" t="n">
+        <v>0</v>
+      </c>
+      <c r="J315" t="n">
         <v>353794.166</v>
       </c>
-      <c r="J315" t="n">
+      <c r="K315" t="n">
         <v>355931.049</v>
       </c>
     </row>
@@ -10551,16 +11505,16 @@
         <v>315</v>
       </c>
       <c r="B316" s="2" t="n">
-        <v>1118.653</v>
+        <v>1117.048</v>
       </c>
       <c r="C316" s="2" t="n">
         <v>1119.16</v>
       </c>
       <c r="D316" s="2" t="n">
-        <v>1119.2</v>
+        <v>1115.55</v>
       </c>
       <c r="E316" s="2" t="n">
-        <v>1118.32</v>
+        <v>1115.55</v>
       </c>
       <c r="F316" s="2" t="n">
         <v>1117.93</v>
@@ -10572,9 +11526,12 @@
         <v>2</v>
       </c>
       <c r="I316" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J316" s="2" t="n">
         <v>353749.166</v>
       </c>
-      <c r="J316" s="2" t="n">
+      <c r="K316" s="2" t="n">
         <v>355928.049</v>
       </c>
     </row>
@@ -10583,19 +11540,19 @@
         <v>316</v>
       </c>
       <c r="B317" s="2" t="n">
-        <v>1118.632</v>
+        <v>1115.55</v>
       </c>
       <c r="C317" s="2" t="n">
-        <v>1119.2</v>
+        <v>1115.55</v>
       </c>
       <c r="D317" s="2" t="n">
-        <v>1118.99</v>
+        <v>1115.55</v>
       </c>
       <c r="E317" s="2" t="n">
-        <v>1118.02</v>
+        <v>1115.55</v>
       </c>
       <c r="F317" s="2" t="n">
-        <v>1118.32</v>
+        <v>1115.55</v>
       </c>
       <c r="G317" s="2" t="n">
         <v>9</v>
@@ -10604,9 +11561,12 @@
         <v>4</v>
       </c>
       <c r="I317" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J317" s="2" t="n">
         <v>353752.166</v>
       </c>
-      <c r="J317" s="2" t="n">
+      <c r="K317" s="2" t="n">
         <v>355928.049</v>
       </c>
     </row>
@@ -10615,19 +11575,19 @@
         <v>317</v>
       </c>
       <c r="B318" s="2" t="n">
-        <v>1118.389</v>
+        <v>1115.55</v>
       </c>
       <c r="C318" s="2" t="n">
-        <v>1118.99</v>
+        <v>1115.55</v>
       </c>
       <c r="D318" s="2" t="n">
-        <v>1118.73</v>
+        <v>1115.55</v>
       </c>
       <c r="E318" s="2" t="n">
-        <v>1117.82</v>
+        <v>1115.55</v>
       </c>
       <c r="F318" s="2" t="n">
-        <v>1118.02</v>
+        <v>1115.55</v>
       </c>
       <c r="G318" s="2" t="n">
         <v>9</v>
@@ -10636,9 +11596,12 @@
         <v>4</v>
       </c>
       <c r="I318" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J318" s="2" t="n">
         <v>353755.166</v>
       </c>
-      <c r="J318" s="2" t="n">
+      <c r="K318" s="2" t="n">
         <v>355928.049</v>
       </c>
     </row>
@@ -10647,19 +11610,19 @@
         <v>318</v>
       </c>
       <c r="B319" s="2" t="n">
-        <v>1118.152</v>
+        <v>1115.55</v>
       </c>
       <c r="C319" s="2" t="n">
-        <v>1118.73</v>
+        <v>1115.55</v>
       </c>
       <c r="D319" s="2" t="n">
-        <v>1118.47</v>
+        <v>1115.55</v>
       </c>
       <c r="E319" s="2" t="n">
-        <v>1117.59</v>
+        <v>1115.55</v>
       </c>
       <c r="F319" s="2" t="n">
-        <v>1117.82</v>
+        <v>1115.55</v>
       </c>
       <c r="G319" s="2" t="n">
         <v>9</v>
@@ -10668,9 +11631,12 @@
         <v>4</v>
       </c>
       <c r="I319" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J319" s="2" t="n">
         <v>353758.166</v>
       </c>
-      <c r="J319" s="2" t="n">
+      <c r="K319" s="2" t="n">
         <v>355928.049</v>
       </c>
     </row>
@@ -10679,19 +11645,19 @@
         <v>319</v>
       </c>
       <c r="B320" s="2" t="n">
-        <v>1117.901</v>
+        <v>1115.55</v>
       </c>
       <c r="C320" s="2" t="n">
-        <v>1118.47</v>
+        <v>1115.55</v>
       </c>
       <c r="D320" s="2" t="n">
-        <v>1118.21</v>
+        <v>1115.55</v>
       </c>
       <c r="E320" s="2" t="n">
-        <v>1117.34</v>
+        <v>1115.55</v>
       </c>
       <c r="F320" s="2" t="n">
-        <v>1117.59</v>
+        <v>1115.55</v>
       </c>
       <c r="G320" s="2" t="n">
         <v>9</v>
@@ -10700,9 +11666,12 @@
         <v>4</v>
       </c>
       <c r="I320" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J320" s="2" t="n">
         <v>353761.166</v>
       </c>
-      <c r="J320" s="2" t="n">
+      <c r="K320" s="2" t="n">
         <v>355928.049</v>
       </c>
     </row>
@@ -10711,19 +11680,19 @@
         <v>320</v>
       </c>
       <c r="B321" s="2" t="n">
-        <v>1117.641</v>
+        <v>1115.55</v>
       </c>
       <c r="C321" s="2" t="n">
-        <v>1118.21</v>
+        <v>1115.55</v>
       </c>
       <c r="D321" s="2" t="n">
-        <v>1117.94</v>
+        <v>1115.55</v>
       </c>
       <c r="E321" s="2" t="n">
-        <v>1117.08</v>
+        <v>1115.55</v>
       </c>
       <c r="F321" s="2" t="n">
-        <v>1117.34</v>
+        <v>1115.55</v>
       </c>
       <c r="G321" s="2" t="n">
         <v>9</v>
@@ -10732,9 +11701,12 @@
         <v>4</v>
       </c>
       <c r="I321" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J321" s="2" t="n">
         <v>353764.166</v>
       </c>
-      <c r="J321" s="2" t="n">
+      <c r="K321" s="2" t="n">
         <v>355928.049</v>
       </c>
     </row>
@@ -10743,19 +11715,19 @@
         <v>321</v>
       </c>
       <c r="B322" s="2" t="n">
-        <v>1117.589</v>
+        <v>1115.55</v>
       </c>
       <c r="C322" s="2" t="n">
-        <v>1117.94</v>
+        <v>1115.55</v>
       </c>
       <c r="D322" s="2" t="n">
-        <v>1117.87</v>
+        <v>1115.55</v>
       </c>
       <c r="E322" s="2" t="n">
-        <v>1117.47</v>
+        <v>1115.55</v>
       </c>
       <c r="F322" s="2" t="n">
-        <v>1117.08</v>
+        <v>1115.55</v>
       </c>
       <c r="G322" s="2" t="n">
         <v>9</v>
@@ -10764,9 +11736,12 @@
         <v>4</v>
       </c>
       <c r="I322" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J322" s="2" t="n">
         <v>353767.166</v>
       </c>
-      <c r="J322" s="2" t="n">
+      <c r="K322" s="2" t="n">
         <v>355928.049</v>
       </c>
     </row>
@@ -10775,10 +11750,10 @@
         <v>322</v>
       </c>
       <c r="B323" s="2" t="n">
-        <v>1118.34</v>
+        <v>1117.281</v>
       </c>
       <c r="C323" s="2" t="n">
-        <v>1117.87</v>
+        <v>1115.55</v>
       </c>
       <c r="D323" s="2" t="n">
         <v>1119.09</v>
@@ -10787,7 +11762,7 @@
         <v>1118.94</v>
       </c>
       <c r="F323" s="2" t="n">
-        <v>1117.47</v>
+        <v>1115.55</v>
       </c>
       <c r="G323" s="2" t="n">
         <v>9</v>
@@ -10796,9 +11771,12 @@
         <v>2</v>
       </c>
       <c r="I323" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J323" s="2" t="n">
         <v>353770.166</v>
       </c>
-      <c r="J323" s="2" t="n">
+      <c r="K323" s="2" t="n">
         <v>355928.049</v>
       </c>
     </row>
@@ -10828,9 +11806,12 @@
         <v>0</v>
       </c>
       <c r="I324" t="n">
+        <v>0</v>
+      </c>
+      <c r="J324" t="n">
         <v>353773.166</v>
       </c>
-      <c r="J324" t="n">
+      <c r="K324" t="n">
         <v>355928.049</v>
       </c>
     </row>
@@ -10860,9 +11841,12 @@
         <v>0</v>
       </c>
       <c r="I325" t="n">
+        <v>0</v>
+      </c>
+      <c r="J325" t="n">
         <v>353776.166</v>
       </c>
-      <c r="J325" t="n">
+      <c r="K325" t="n">
         <v>355928.049</v>
       </c>
     </row>
@@ -10892,9 +11876,12 @@
         <v>0</v>
       </c>
       <c r="I326" t="n">
+        <v>0</v>
+      </c>
+      <c r="J326" t="n">
         <v>353779.166</v>
       </c>
-      <c r="J326" t="n">
+      <c r="K326" t="n">
         <v>355928.049</v>
       </c>
     </row>
@@ -10924,9 +11911,12 @@
         <v>0</v>
       </c>
       <c r="I327" t="n">
+        <v>0</v>
+      </c>
+      <c r="J327" t="n">
         <v>353782.166</v>
       </c>
-      <c r="J327" t="n">
+      <c r="K327" t="n">
         <v>355928.049</v>
       </c>
     </row>
@@ -10956,9 +11946,12 @@
         <v>0</v>
       </c>
       <c r="I328" t="n">
+        <v>0</v>
+      </c>
+      <c r="J328" t="n">
         <v>353785.166</v>
       </c>
-      <c r="J328" t="n">
+      <c r="K328" t="n">
         <v>355928.049</v>
       </c>
     </row>
@@ -10988,9 +11981,12 @@
         <v>0</v>
       </c>
       <c r="I329" t="n">
+        <v>0</v>
+      </c>
+      <c r="J329" t="n">
         <v>353788.166</v>
       </c>
-      <c r="J329" t="n">
+      <c r="K329" t="n">
         <v>355928.049</v>
       </c>
     </row>
@@ -11020,9 +12016,12 @@
         <v>0</v>
       </c>
       <c r="I330" t="n">
+        <v>0</v>
+      </c>
+      <c r="J330" t="n">
         <v>353791.166</v>
       </c>
-      <c r="J330" t="n">
+      <c r="K330" t="n">
         <v>355928.049</v>
       </c>
     </row>
@@ -11052,9 +12051,12 @@
         <v>0</v>
       </c>
       <c r="I331" t="n">
+        <v>0</v>
+      </c>
+      <c r="J331" t="n">
         <v>353794.166</v>
       </c>
-      <c r="J331" t="n">
+      <c r="K331" t="n">
         <v>355928.049</v>
       </c>
     </row>
@@ -11063,16 +12065,16 @@
         <v>331</v>
       </c>
       <c r="B332" s="2" t="n">
-        <v>1117.534</v>
+        <v>1116.573</v>
       </c>
       <c r="C332" s="2" t="n">
         <v>1117.93</v>
       </c>
       <c r="D332" s="2" t="n">
-        <v>1118.32</v>
+        <v>1115.55</v>
       </c>
       <c r="E332" s="2" t="n">
-        <v>1116.62</v>
+        <v>1115.55</v>
       </c>
       <c r="F332" s="2" t="n">
         <v>1117.26</v>
@@ -11084,9 +12086,12 @@
         <v>2</v>
       </c>
       <c r="I332" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J332" s="2" t="n">
         <v>353749.166</v>
       </c>
-      <c r="J332" s="2" t="n">
+      <c r="K332" s="2" t="n">
         <v>355925.049</v>
       </c>
     </row>
@@ -11095,19 +12100,19 @@
         <v>332</v>
       </c>
       <c r="B333" s="2" t="n">
-        <v>1117.612</v>
+        <v>1115.55</v>
       </c>
       <c r="C333" s="2" t="n">
-        <v>1118.32</v>
+        <v>1115.55</v>
       </c>
       <c r="D333" s="2" t="n">
-        <v>1118.02</v>
+        <v>1115.55</v>
       </c>
       <c r="E333" s="2" t="n">
-        <v>1117.48</v>
+        <v>1115.55</v>
       </c>
       <c r="F333" s="2" t="n">
-        <v>1116.62</v>
+        <v>1115.55</v>
       </c>
       <c r="G333" s="2" t="n">
         <v>9</v>
@@ -11116,9 +12121,12 @@
         <v>4</v>
       </c>
       <c r="I333" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J333" s="2" t="n">
         <v>353752.166</v>
       </c>
-      <c r="J333" s="2" t="n">
+      <c r="K333" s="2" t="n">
         <v>355925.049</v>
       </c>
     </row>
@@ -11127,19 +12135,19 @@
         <v>333</v>
       </c>
       <c r="B334" s="2" t="n">
-        <v>1117.54</v>
+        <v>1115.55</v>
       </c>
       <c r="C334" s="2" t="n">
-        <v>1118.02</v>
+        <v>1115.55</v>
       </c>
       <c r="D334" s="2" t="n">
-        <v>1117.82</v>
+        <v>1115.55</v>
       </c>
       <c r="E334" s="2" t="n">
-        <v>1116.84</v>
+        <v>1115.55</v>
       </c>
       <c r="F334" s="2" t="n">
-        <v>1117.48</v>
+        <v>1115.55</v>
       </c>
       <c r="G334" s="2" t="n">
         <v>9</v>
@@ -11148,9 +12156,12 @@
         <v>4</v>
       </c>
       <c r="I334" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J334" s="2" t="n">
         <v>353755.166</v>
       </c>
-      <c r="J334" s="2" t="n">
+      <c r="K334" s="2" t="n">
         <v>355925.049</v>
       </c>
     </row>
@@ -11159,19 +12170,19 @@
         <v>334</v>
       </c>
       <c r="B335" s="2" t="n">
-        <v>1117.225</v>
+        <v>1115.55</v>
       </c>
       <c r="C335" s="2" t="n">
-        <v>1117.82</v>
+        <v>1115.55</v>
       </c>
       <c r="D335" s="2" t="n">
-        <v>1117.59</v>
+        <v>1115.55</v>
       </c>
       <c r="E335" s="2" t="n">
-        <v>1116.65</v>
+        <v>1115.55</v>
       </c>
       <c r="F335" s="2" t="n">
-        <v>1116.84</v>
+        <v>1115.55</v>
       </c>
       <c r="G335" s="2" t="n">
         <v>9</v>
@@ -11180,9 +12191,12 @@
         <v>4</v>
       </c>
       <c r="I335" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J335" s="2" t="n">
         <v>353758.166</v>
       </c>
-      <c r="J335" s="2" t="n">
+      <c r="K335" s="2" t="n">
         <v>355925.049</v>
       </c>
     </row>
@@ -11191,19 +12205,19 @@
         <v>335</v>
       </c>
       <c r="B336" s="2" t="n">
-        <v>1117.001</v>
+        <v>1115.55</v>
       </c>
       <c r="C336" s="2" t="n">
-        <v>1117.59</v>
+        <v>1115.55</v>
       </c>
       <c r="D336" s="2" t="n">
-        <v>1117.34</v>
+        <v>1115.55</v>
       </c>
       <c r="E336" s="2" t="n">
-        <v>1116.42</v>
+        <v>1115.55</v>
       </c>
       <c r="F336" s="2" t="n">
-        <v>1116.65</v>
+        <v>1115.55</v>
       </c>
       <c r="G336" s="2" t="n">
         <v>9</v>
@@ -11212,9 +12226,12 @@
         <v>4</v>
       </c>
       <c r="I336" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J336" s="2" t="n">
         <v>353761.166</v>
       </c>
-      <c r="J336" s="2" t="n">
+      <c r="K336" s="2" t="n">
         <v>355925.049</v>
       </c>
     </row>
@@ -11223,19 +12240,19 @@
         <v>336</v>
       </c>
       <c r="B337" s="2" t="n">
-        <v>1116.758</v>
+        <v>1115.55</v>
       </c>
       <c r="C337" s="2" t="n">
-        <v>1117.34</v>
+        <v>1115.55</v>
       </c>
       <c r="D337" s="2" t="n">
-        <v>1117.08</v>
+        <v>1115.55</v>
       </c>
       <c r="E337" s="2" t="n">
-        <v>1116.2</v>
+        <v>1115.55</v>
       </c>
       <c r="F337" s="2" t="n">
-        <v>1116.42</v>
+        <v>1115.55</v>
       </c>
       <c r="G337" s="2" t="n">
         <v>9</v>
@@ -11244,9 +12261,12 @@
         <v>4</v>
       </c>
       <c r="I337" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J337" s="2" t="n">
         <v>353764.166</v>
       </c>
-      <c r="J337" s="2" t="n">
+      <c r="K337" s="2" t="n">
         <v>355925.049</v>
       </c>
     </row>
@@ -11255,19 +12275,19 @@
         <v>337</v>
       </c>
       <c r="B338" s="2" t="n">
-        <v>1117.008</v>
+        <v>1115.985</v>
       </c>
       <c r="C338" s="2" t="n">
-        <v>1117.08</v>
+        <v>1115.55</v>
       </c>
       <c r="D338" s="2" t="n">
-        <v>1117.47</v>
+        <v>1115.55</v>
       </c>
       <c r="E338" s="2" t="n">
         <v>1117.29</v>
       </c>
       <c r="F338" s="2" t="n">
-        <v>1116.2</v>
+        <v>1115.55</v>
       </c>
       <c r="G338" s="2" t="n">
         <v>9</v>
@@ -11276,9 +12296,12 @@
         <v>3</v>
       </c>
       <c r="I338" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J338" s="2" t="n">
         <v>353767.166</v>
       </c>
-      <c r="J338" s="2" t="n">
+      <c r="K338" s="2" t="n">
         <v>355925.049</v>
       </c>
     </row>
@@ -11287,10 +12310,10 @@
         <v>338</v>
       </c>
       <c r="B339" s="2" t="n">
-        <v>1118.143</v>
+        <v>1117.663</v>
       </c>
       <c r="C339" s="2" t="n">
-        <v>1117.47</v>
+        <v>1115.55</v>
       </c>
       <c r="D339" s="2" t="n">
         <v>1118.94</v>
@@ -11308,9 +12331,12 @@
         <v>1</v>
       </c>
       <c r="I339" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J339" s="2" t="n">
         <v>353770.166</v>
       </c>
-      <c r="J339" s="2" t="n">
+      <c r="K339" s="2" t="n">
         <v>355925.049</v>
       </c>
     </row>
@@ -11340,9 +12366,12 @@
         <v>0</v>
       </c>
       <c r="I340" t="n">
+        <v>0</v>
+      </c>
+      <c r="J340" t="n">
         <v>353773.166</v>
       </c>
-      <c r="J340" t="n">
+      <c r="K340" t="n">
         <v>355925.049</v>
       </c>
     </row>
@@ -11372,9 +12401,12 @@
         <v>0</v>
       </c>
       <c r="I341" t="n">
+        <v>0</v>
+      </c>
+      <c r="J341" t="n">
         <v>353776.166</v>
       </c>
-      <c r="J341" t="n">
+      <c r="K341" t="n">
         <v>355925.049</v>
       </c>
     </row>
@@ -11404,9 +12436,12 @@
         <v>0</v>
       </c>
       <c r="I342" t="n">
+        <v>0</v>
+      </c>
+      <c r="J342" t="n">
         <v>353779.166</v>
       </c>
-      <c r="J342" t="n">
+      <c r="K342" t="n">
         <v>355925.049</v>
       </c>
     </row>
@@ -11436,9 +12471,12 @@
         <v>0</v>
       </c>
       <c r="I343" t="n">
+        <v>0</v>
+      </c>
+      <c r="J343" t="n">
         <v>353782.166</v>
       </c>
-      <c r="J343" t="n">
+      <c r="K343" t="n">
         <v>355925.049</v>
       </c>
     </row>
@@ -11468,9 +12506,12 @@
         <v>0</v>
       </c>
       <c r="I344" t="n">
+        <v>0</v>
+      </c>
+      <c r="J344" t="n">
         <v>353785.166</v>
       </c>
-      <c r="J344" t="n">
+      <c r="K344" t="n">
         <v>355925.049</v>
       </c>
     </row>
@@ -11500,9 +12541,12 @@
         <v>0</v>
       </c>
       <c r="I345" t="n">
+        <v>0</v>
+      </c>
+      <c r="J345" t="n">
         <v>353788.166</v>
       </c>
-      <c r="J345" t="n">
+      <c r="K345" t="n">
         <v>355925.049</v>
       </c>
     </row>
@@ -11532,9 +12576,12 @@
         <v>0</v>
       </c>
       <c r="I346" t="n">
+        <v>0</v>
+      </c>
+      <c r="J346" t="n">
         <v>353791.166</v>
       </c>
-      <c r="J346" t="n">
+      <c r="K346" t="n">
         <v>355925.049</v>
       </c>
     </row>
@@ -11543,13 +12590,13 @@
         <v>346</v>
       </c>
       <c r="B347" s="2" t="n">
-        <v>1117.011</v>
+        <v>1116.743</v>
       </c>
       <c r="C347" s="2" t="n">
         <v>1117.26</v>
       </c>
       <c r="D347" s="2" t="n">
-        <v>1116.62</v>
+        <v>1115.55</v>
       </c>
       <c r="E347" s="2" t="n">
         <v>1116.46</v>
@@ -11564,9 +12611,12 @@
         <v>1</v>
       </c>
       <c r="I347" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J347" s="2" t="n">
         <v>353749.166</v>
       </c>
-      <c r="J347" s="2" t="n">
+      <c r="K347" s="2" t="n">
         <v>355922.049</v>
       </c>
     </row>
@@ -11575,13 +12625,13 @@
         <v>347</v>
       </c>
       <c r="B348" s="2" t="n">
-        <v>1116.821</v>
+        <v>1116.069</v>
       </c>
       <c r="C348" s="2" t="n">
-        <v>1116.62</v>
+        <v>1115.55</v>
       </c>
       <c r="D348" s="2" t="n">
-        <v>1117.48</v>
+        <v>1115.55</v>
       </c>
       <c r="E348" s="2" t="n">
         <v>1116.71</v>
@@ -11596,9 +12646,12 @@
         <v>2</v>
       </c>
       <c r="I348" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J348" s="2" t="n">
         <v>353752.166</v>
       </c>
-      <c r="J348" s="2" t="n">
+      <c r="K348" s="2" t="n">
         <v>355922.049</v>
       </c>
     </row>
@@ -11607,13 +12660,13 @@
         <v>348</v>
       </c>
       <c r="B349" s="2" t="n">
-        <v>1116.92</v>
+        <v>1116.115</v>
       </c>
       <c r="C349" s="2" t="n">
-        <v>1117.48</v>
+        <v>1115.55</v>
       </c>
       <c r="D349" s="2" t="n">
-        <v>1116.84</v>
+        <v>1115.55</v>
       </c>
       <c r="E349" s="2" t="n">
         <v>1116.65</v>
@@ -11628,9 +12681,12 @@
         <v>2</v>
       </c>
       <c r="I349" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J349" s="2" t="n">
         <v>353755.166</v>
       </c>
-      <c r="J349" s="2" t="n">
+      <c r="K349" s="2" t="n">
         <v>355922.049</v>
       </c>
     </row>
@@ -11639,13 +12695,13 @@
         <v>349</v>
       </c>
       <c r="B350" s="2" t="n">
-        <v>1116.572</v>
+        <v>1115.974</v>
       </c>
       <c r="C350" s="2" t="n">
-        <v>1116.84</v>
+        <v>1115.55</v>
       </c>
       <c r="D350" s="2" t="n">
-        <v>1116.65</v>
+        <v>1115.55</v>
       </c>
       <c r="E350" s="2" t="n">
         <v>1116.15</v>
@@ -11660,9 +12716,12 @@
         <v>2</v>
       </c>
       <c r="I350" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J350" s="2" t="n">
         <v>353758.166</v>
       </c>
-      <c r="J350" s="2" t="n">
+      <c r="K350" s="2" t="n">
         <v>355922.049</v>
       </c>
     </row>
@@ -11671,13 +12730,13 @@
         <v>350</v>
       </c>
       <c r="B351" s="2" t="n">
-        <v>1116.819</v>
+        <v>1116.325</v>
       </c>
       <c r="C351" s="2" t="n">
-        <v>1116.65</v>
+        <v>1115.55</v>
       </c>
       <c r="D351" s="2" t="n">
-        <v>1116.42</v>
+        <v>1115.55</v>
       </c>
       <c r="E351" s="2" t="n">
         <v>1118.05</v>
@@ -11692,9 +12751,12 @@
         <v>2</v>
       </c>
       <c r="I351" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J351" s="2" t="n">
         <v>353761.166</v>
       </c>
-      <c r="J351" s="2" t="n">
+      <c r="K351" s="2" t="n">
         <v>355922.049</v>
       </c>
     </row>
@@ -11703,13 +12765,13 @@
         <v>351</v>
       </c>
       <c r="B352" s="2" t="n">
-        <v>1117.442</v>
+        <v>1117.062</v>
       </c>
       <c r="C352" s="2" t="n">
-        <v>1116.42</v>
+        <v>1115.55</v>
       </c>
       <c r="D352" s="2" t="n">
-        <v>1116.2</v>
+        <v>1115.55</v>
       </c>
       <c r="E352" s="2" t="n">
         <v>1119.1</v>
@@ -11724,9 +12786,12 @@
         <v>2</v>
       </c>
       <c r="I352" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J352" s="2" t="n">
         <v>353764.166</v>
       </c>
-      <c r="J352" s="2" t="n">
+      <c r="K352" s="2" t="n">
         <v>355922.049</v>
       </c>
     </row>
@@ -11735,10 +12800,10 @@
         <v>352</v>
       </c>
       <c r="B353" s="2" t="n">
-        <v>1117.905</v>
+        <v>1117.744</v>
       </c>
       <c r="C353" s="2" t="n">
-        <v>1116.2</v>
+        <v>1115.55</v>
       </c>
       <c r="D353" s="2" t="n">
         <v>1117.29</v>
@@ -11756,9 +12821,12 @@
         <v>1</v>
       </c>
       <c r="I353" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J353" s="2" t="n">
         <v>353767.166</v>
       </c>
-      <c r="J353" s="2" t="n">
+      <c r="K353" s="2" t="n">
         <v>355922.049</v>
       </c>
     </row>
@@ -11788,9 +12856,12 @@
         <v>0</v>
       </c>
       <c r="I354" t="n">
+        <v>0</v>
+      </c>
+      <c r="J354" t="n">
         <v>353770.166</v>
       </c>
-      <c r="J354" t="n">
+      <c r="K354" t="n">
         <v>355922.049</v>
       </c>
     </row>
@@ -11820,9 +12891,12 @@
         <v>0</v>
       </c>
       <c r="I355" t="n">
+        <v>0</v>
+      </c>
+      <c r="J355" t="n">
         <v>353773.166</v>
       </c>
-      <c r="J355" t="n">
+      <c r="K355" t="n">
         <v>355922.049</v>
       </c>
     </row>
@@ -11852,9 +12926,12 @@
         <v>0</v>
       </c>
       <c r="I356" t="n">
+        <v>0</v>
+      </c>
+      <c r="J356" t="n">
         <v>353776.166</v>
       </c>
-      <c r="J356" t="n">
+      <c r="K356" t="n">
         <v>355922.049</v>
       </c>
     </row>
@@ -11884,9 +12961,12 @@
         <v>0</v>
       </c>
       <c r="I357" t="n">
+        <v>0</v>
+      </c>
+      <c r="J357" t="n">
         <v>353779.166</v>
       </c>
-      <c r="J357" t="n">
+      <c r="K357" t="n">
         <v>355922.049</v>
       </c>
     </row>
@@ -11916,9 +12996,12 @@
         <v>0</v>
       </c>
       <c r="I358" t="n">
+        <v>0</v>
+      </c>
+      <c r="J358" t="n">
         <v>353782.166</v>
       </c>
-      <c r="J358" t="n">
+      <c r="K358" t="n">
         <v>355922.049</v>
       </c>
     </row>
@@ -11948,9 +13031,12 @@
         <v>0</v>
       </c>
       <c r="I359" t="n">
+        <v>0</v>
+      </c>
+      <c r="J359" t="n">
         <v>353785.166</v>
       </c>
-      <c r="J359" t="n">
+      <c r="K359" t="n">
         <v>355922.049</v>
       </c>
     </row>
@@ -11980,9 +13066,12 @@
         <v>0</v>
       </c>
       <c r="I360" t="n">
+        <v>0</v>
+      </c>
+      <c r="J360" t="n">
         <v>353788.166</v>
       </c>
-      <c r="J360" t="n">
+      <c r="K360" t="n">
         <v>355922.049</v>
       </c>
     </row>
@@ -12012,9 +13101,12 @@
         <v>0</v>
       </c>
       <c r="I361" t="n">
+        <v>0</v>
+      </c>
+      <c r="J361" t="n">
         <v>353752.166</v>
       </c>
-      <c r="J361" t="n">
+      <c r="K361" t="n">
         <v>355919.049</v>
       </c>
     </row>
@@ -12044,9 +13136,12 @@
         <v>0</v>
       </c>
       <c r="I362" t="n">
+        <v>0</v>
+      </c>
+      <c r="J362" t="n">
         <v>353755.166</v>
       </c>
-      <c r="J362" t="n">
+      <c r="K362" t="n">
         <v>355919.049</v>
       </c>
     </row>
@@ -12076,9 +13171,12 @@
         <v>0</v>
       </c>
       <c r="I363" t="n">
+        <v>0</v>
+      </c>
+      <c r="J363" t="n">
         <v>353758.166</v>
       </c>
-      <c r="J363" t="n">
+      <c r="K363" t="n">
         <v>355919.049</v>
       </c>
     </row>
@@ -12108,9 +13206,12 @@
         <v>0</v>
       </c>
       <c r="I364" t="n">
+        <v>0</v>
+      </c>
+      <c r="J364" t="n">
         <v>353761.166</v>
       </c>
-      <c r="J364" t="n">
+      <c r="K364" t="n">
         <v>355919.049</v>
       </c>
     </row>
@@ -12140,9 +13241,12 @@
         <v>0</v>
       </c>
       <c r="I365" t="n">
+        <v>0</v>
+      </c>
+      <c r="J365" t="n">
         <v>353764.166</v>
       </c>
-      <c r="J365" t="n">
+      <c r="K365" t="n">
         <v>355919.049</v>
       </c>
     </row>
@@ -12172,9 +13276,12 @@
         <v>0</v>
       </c>
       <c r="I366" t="n">
+        <v>0</v>
+      </c>
+      <c r="J366" t="n">
         <v>353767.166</v>
       </c>
-      <c r="J366" t="n">
+      <c r="K366" t="n">
         <v>355919.049</v>
       </c>
     </row>
@@ -12204,9 +13311,12 @@
         <v>0</v>
       </c>
       <c r="I367" t="n">
+        <v>0</v>
+      </c>
+      <c r="J367" t="n">
         <v>353770.166</v>
       </c>
-      <c r="J367" t="n">
+      <c r="K367" t="n">
         <v>355919.049</v>
       </c>
     </row>
@@ -12236,9 +13346,12 @@
         <v>0</v>
       </c>
       <c r="I368" t="n">
+        <v>0</v>
+      </c>
+      <c r="J368" t="n">
         <v>353773.166</v>
       </c>
-      <c r="J368" t="n">
+      <c r="K368" t="n">
         <v>355919.049</v>
       </c>
     </row>
@@ -12268,9 +13381,12 @@
         <v>0</v>
       </c>
       <c r="I369" t="n">
+        <v>0</v>
+      </c>
+      <c r="J369" t="n">
         <v>353776.166</v>
       </c>
-      <c r="J369" t="n">
+      <c r="K369" t="n">
         <v>355919.049</v>
       </c>
     </row>
@@ -12300,9 +13416,12 @@
         <v>0</v>
       </c>
       <c r="I370" t="n">
+        <v>0</v>
+      </c>
+      <c r="J370" t="n">
         <v>353779.166</v>
       </c>
-      <c r="J370" t="n">
+      <c r="K370" t="n">
         <v>355919.049</v>
       </c>
     </row>
@@ -12332,9 +13451,12 @@
         <v>0</v>
       </c>
       <c r="I371" t="n">
+        <v>0</v>
+      </c>
+      <c r="J371" t="n">
         <v>353782.166</v>
       </c>
-      <c r="J371" t="n">
+      <c r="K371" t="n">
         <v>355919.049</v>
       </c>
     </row>
@@ -12364,9 +13486,12 @@
         <v>0</v>
       </c>
       <c r="I372" t="n">
+        <v>0</v>
+      </c>
+      <c r="J372" t="n">
         <v>353785.166</v>
       </c>
-      <c r="J372" t="n">
+      <c r="K372" t="n">
         <v>355919.049</v>
       </c>
     </row>
@@ -12396,9 +13521,12 @@
         <v>0</v>
       </c>
       <c r="I373" t="n">
+        <v>0</v>
+      </c>
+      <c r="J373" t="n">
         <v>353788.166</v>
       </c>
-      <c r="J373" t="n">
+      <c r="K373" t="n">
         <v>355919.049</v>
       </c>
     </row>
@@ -12448,7 +13576,14 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Yellow rows: one or more corners had no EL label and were interpolated from the survey TIN.</t>
+          <t>Yellow rows: one or more corners inside the hangar area, taken as 1115.55.</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Orange rows: one corner had no EL label and was interpolated from the survey TIN.</t>
         </is>
       </c>
     </row>
